--- a/[MSIM4310]-analisis-dan-visualisasi-data/pertemuan-08/data_pendapatan.xlsx
+++ b/[MSIM4310]-analisis-dan-visualisasi-data/pertemuan-08/data_pendapatan.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PRODI\MSIM4310\KIT Tutorial MSIM4310 Analisis dan Visualisasi Data (AVD)\KIT Tutorial MSIM4310 Analisis dan Visualisasi Data (AVD)\Tugas AVD\Tugas 2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{045C2DE5-2271-42B3-A101-2B847AB6303F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{11DF51BD-97B6-419A-909E-A65F37A5FC3E}"/>
+    <workbookView windowWidth="28800" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="data.pendapatan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>no</t>
   </si>
@@ -30,117 +37,76 @@
   <si>
     <t>kebahagiaan</t>
   </si>
-  <si>
-    <t>0.953412996</t>
-  </si>
-  <si>
-    <t>0.97288292</t>
-  </si>
-  <si>
-    <t>0.669715948</t>
-  </si>
-  <si>
-    <t>0.859499052</t>
-  </si>
-  <si>
-    <t>0.727221191</t>
-  </si>
-  <si>
-    <t>0.771286567</t>
-  </si>
-  <si>
-    <t>0.258722097</t>
-  </si>
-  <si>
-    <t>0.458377574</t>
-  </si>
-  <si>
-    <t>0.992917365</t>
-  </si>
-  <si>
-    <t>0.987603172</t>
-  </si>
-  <si>
-    <t>0.438171567</t>
-  </si>
-  <si>
-    <t>0.688090581</t>
-  </si>
-  <si>
-    <t>0.971332454</t>
-  </si>
-  <si>
-    <t>0.968527327</t>
-  </si>
-  <si>
-    <t>0.628942061</t>
-  </si>
-  <si>
-    <t>0.654242148</t>
-  </si>
-  <si>
-    <t>0.686920849</t>
-  </si>
-  <si>
-    <t>0.846505526</t>
-  </si>
-  <si>
-    <t>0.73163629</t>
-  </si>
-  <si>
-    <t>0.898732803</t>
-  </si>
-  <si>
-    <t>0.546190176</t>
-  </si>
-  <si>
-    <t>0.266043663</t>
-  </si>
-  <si>
-    <t>0.698459965</t>
-  </si>
-  <si>
-    <t>0.688909231</t>
-  </si>
-  <si>
-    <t>0.685848874</t>
-  </si>
-  <si>
-    <t>0.548365189</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Aptos Display"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -148,7 +114,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -156,35 +122,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -192,7 +137,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -200,14 +145,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -215,22 +153,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -238,14 +168,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -258,175 +209,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,6 +400,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -461,7 +440,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -496,15 +475,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -520,17 +490,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -546,109 +510,134 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -697,7 +686,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -730,26 +719,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -782,23 +754,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -960,26 +915,21 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E80675-062F-48D6-8FF1-0B4A73483120}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C499"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.81730769230769" style="1" customWidth="1"/>
+    <col min="2" max="3" width="12.4519230769231" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -989,5485 +939,5486 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>3626474184</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>2314488983</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>4793813825</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>3233489759</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>4920956936</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>4599373404</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>3214372439</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>2661113803</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>7246409251</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>5596398273</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>3729643479</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>2458555872</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>4564517389</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>3342991809</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>4698103821</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>1907136833</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>3221630526</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>2942449872</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>4639914435</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>3737941605</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>4632839514</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>3165406147</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+    <row r="13" spans="1:3">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>2773178895</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>2009046461</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>7119478595</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>5951814099</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+    <row r="15" spans="1:3">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>7476653196</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>5950547308</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+    <row r="16" spans="1:3">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <v>2177423312</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>1445798858</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+    <row r="17" spans="1:3">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <v>2591658195</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>2898583142</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+    <row r="18" spans="1:3">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>235479322</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>1231167524</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+    <row r="19" spans="1:3">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>2381572476</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>2312988055</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+    <row r="20" spans="1:3">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>4655680274</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>2666116035</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+    <row r="21" spans="1:3">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>1884275047</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>2584729022</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+    <row r="22" spans="1:3">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <v>7410916026</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>5747444104</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+    <row r="23" spans="1:3">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2">
         <v>4528318956</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2">
         <v>2546524587</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+    <row r="24" spans="1:3">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2">
         <v>2528751675</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2">
         <v>1200785525</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+    <row r="25" spans="1:3">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="2">
         <v>3442747875</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2">
         <v>3078293381</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+    <row r="26" spans="1:3">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2">
         <v>5227201239</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="2">
         <v>4317760919</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+    <row r="27" spans="1:3">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2">
         <v>689199314</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="2">
         <v>5381478737</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+    <row r="28" spans="1:3">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2">
         <v>3400409939</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="2">
         <v>3565224319</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+    <row r="29" spans="1:3">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="2">
         <v>2391055478</v>
       </c>
-      <c r="C29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+      <c r="C29" s="3">
+        <v>0.953412996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2">
         <v>2380512706</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="2">
         <v>2169161261</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+    <row r="31" spans="1:3">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="2">
         <v>2549608776</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="2">
         <v>2060794311</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+    <row r="32" spans="1:3">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="2">
         <v>5933295827</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="2">
         <v>6299101259</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+    <row r="33" spans="1:3">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="2">
         <v>1855645173</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="2">
         <v>1560355862</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+    <row r="34" spans="1:3">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="2">
         <v>3489023138</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="2">
         <v>2250929414</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+    <row r="35" spans="1:3">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="2">
         <v>6826477911</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="2">
         <v>59142477</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+    <row r="36" spans="1:3">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="2">
         <v>2040601883</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="2">
         <v>2181833702</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+    <row r="37" spans="1:3">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="2">
         <v>5234205274</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="2">
         <v>5767814366</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+    <row r="38" spans="1:3">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="2">
         <v>224311363</v>
       </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+      <c r="C38" s="3">
+        <v>0.97288292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="2">
         <v>7056166367</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="2">
         <v>5010577427</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+    <row r="40" spans="1:3">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="2">
         <v>4190672496</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="2">
         <v>2239664992</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+    <row r="41" spans="1:3">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="2">
         <v>175648612</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="2">
         <v>1827578829</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+    <row r="42" spans="1:3">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="2">
         <v>5061758185</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="2">
         <v>335807157</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+    <row r="43" spans="1:3">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="2">
         <v>3982189934</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="2">
         <v>2400087291</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+    <row r="44" spans="1:3">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="2">
         <v>306505862</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="2">
         <v>3407980039</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+    <row r="45" spans="1:3">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="2">
         <v>368287749</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="2">
         <v>2576176307</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+    <row r="46" spans="1:3">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="2">
         <v>3789429291</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="2">
         <v>2473079377</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+    <row r="47" spans="1:3">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="2">
         <v>5358715665</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="2">
         <v>3752659492</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
+    <row r="48" spans="1:3">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="2">
         <v>5196119777</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="2">
         <v>4087631183</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+    <row r="49" spans="1:3">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="2">
         <v>5241189571</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="2">
         <v>3543203654</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+    <row r="50" spans="1:3">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="2">
         <v>7101619593</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="2">
         <v>534835294</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+    <row r="51" spans="1:3">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="2">
         <v>3424021093</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="2">
         <v>3056376653</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
+    <row r="52" spans="1:3">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="2">
         <v>2253399021</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="2">
         <v>1558422563</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
+    <row r="53" spans="1:3">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="2">
         <v>5370336904</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="2">
         <v>3225132752</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="2">
+    <row r="54" spans="1:3">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="2">
         <v>6225606</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="2">
         <v>5064231009</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+    <row r="55" spans="1:3">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="2">
         <v>5482862234</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="2">
         <v>3857424259</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="2">
+    <row r="56" spans="1:3">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>4034172109</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>361905549</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="2">
+    <row r="57" spans="1:3">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="2">
         <v>6510218719</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="2">
         <v>4004537739</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="2">
+    <row r="58" spans="1:3">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="2">
         <v>6029213862</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="2">
         <v>4802091807</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="2">
+    <row r="59" spans="1:3">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="2">
         <v>6949112894</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="2">
         <v>4658890392</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="2">
+    <row r="60" spans="1:3">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="2">
         <v>7195037289</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="2">
         <v>5231702968</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="2">
+    <row r="61" spans="1:3">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="2">
         <v>2757338498</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="2">
         <v>2480606467</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="2">
+    <row r="62" spans="1:3">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="2">
         <v>6956079482</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="2">
         <v>5498147193</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="2">
+    <row r="63" spans="1:3">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="2">
         <v>4670192578</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="2">
         <v>4550636958</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="2">
+    <row r="64" spans="1:3">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="2">
         <v>6368292668</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="2">
         <v>3570013567</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="2">
+    <row r="65" spans="1:3">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="2">
         <v>6166681166</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="2">
         <v>4629665333</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="2">
+    <row r="66" spans="1:3">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="2">
         <v>6074158292</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="2">
         <v>4503108168</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="2">
+    <row r="67" spans="1:3">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="2">
         <v>5484718965</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="2">
         <v>5046081775</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="2">
+    <row r="68" spans="1:3">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="2">
         <v>1589574738</v>
       </c>
-      <c r="C68" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="2">
+      <c r="C68" s="3">
+        <v>0.669715948</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="2">
         <v>1680473928</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="2">
         <v>1606072357</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="2">
+    <row r="70" spans="1:3">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="2">
         <v>5499947957</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="2">
         <v>4826602696</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="2">
+    <row r="71" spans="1:3">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="1">
+      <c r="B71" s="2">
         <v>4043890903</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="2">
         <v>2208240516</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="2">
+    <row r="72" spans="1:3">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="B72" s="1">
+      <c r="B72" s="2">
         <v>5005093241</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="2">
         <v>4056493099</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="2">
+    <row r="73" spans="1:3">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="1">
+      <c r="B73" s="2">
         <v>4863581726</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="2">
         <v>3567905233</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="2">
+    <row r="74" spans="1:3">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B74" s="2">
         <v>1506275045</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="2">
         <v>1308487263</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="2">
+    <row r="75" spans="1:3">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B75" s="2">
         <v>2864663845</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="2">
         <v>41596093</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="2">
+    <row r="76" spans="1:3">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="1">
+      <c r="B76" s="2">
         <v>5877906294</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="2">
         <v>4533915057</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="2">
+    <row r="77" spans="1:3">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="1">
+      <c r="B77" s="2">
         <v>6483983789</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="2">
         <v>5068747881</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="2">
+    <row r="78" spans="1:3">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="1">
+      <c r="B78" s="2">
         <v>4938036592</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="2">
         <v>3040797294</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="2">
+    <row r="79" spans="1:3">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B79" s="2">
         <v>5625434421</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="2">
         <v>3804298861</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="2">
+    <row r="80" spans="1:3">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B80" s="2">
         <v>7228265215</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="2">
         <v>5034003785</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="2">
+    <row r="81" spans="1:3">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="1">
+      <c r="B81" s="2">
         <v>5337460294</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="2">
         <v>3703437932</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="2">
+    <row r="82" spans="1:3">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="1">
+      <c r="B82" s="2">
         <v>282582659</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="2">
         <v>2188938121</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="2">
+    <row r="83" spans="1:3">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B83" s="2">
         <v>5931366673</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="2">
         <v>5538047529</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="2">
+    <row r="84" spans="1:3">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="1">
+      <c r="B84" s="2">
         <v>3520255202</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="2">
         <v>3453875162</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="2">
+    <row r="85" spans="1:3">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="1">
+      <c r="B85" s="2">
         <v>3239940593</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="2">
         <v>309688561</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="2">
+    <row r="86" spans="1:3">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="1">
+      <c r="B86" s="2">
         <v>3498386369</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86" s="2">
         <v>2200982172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="2">
+    <row r="87" spans="1:3">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="1">
+      <c r="B87" s="2">
         <v>7186112258</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="2">
         <v>5151598289</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="2">
+    <row r="88" spans="1:3">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="1">
+      <c r="B88" s="2">
         <v>4719166072</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="2">
         <v>5950986328</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="2">
+    <row r="89" spans="1:3">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B89" s="2">
         <v>3594801958</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="2">
         <v>2968187102</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="2">
+    <row r="90" spans="1:3">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="B90" s="1">
+      <c r="B90" s="2">
         <v>3233942432</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="2">
         <v>2399561326</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="2">
+    <row r="91" spans="1:3">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="1">
+      <c r="B91" s="2">
         <v>1514153223</v>
       </c>
-      <c r="C91" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="2">
+      <c r="C91" s="3">
+        <v>0.859499052</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="1">
+      <c r="B92" s="2">
         <v>4002537064</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="2">
         <v>1545932552</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="2">
+    <row r="93" spans="1:3">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="B93" s="1">
+      <c r="B93" s="2">
         <v>619810376</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="2">
         <v>4661261209</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="2">
+    <row r="94" spans="1:3">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="1">
+      <c r="B94" s="2">
         <v>2280650861</v>
       </c>
-      <c r="C94" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="2">
+      <c r="C94" s="3">
+        <v>0.727221191</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="1">
+      <c r="B95" s="2">
         <v>2189865512</v>
       </c>
-      <c r="C95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="2">
+      <c r="C95" s="3">
+        <v>0.771286567</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="B96" s="1">
+      <c r="B96" s="2">
         <v>3434151134</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="2">
         <v>3348788206</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="2">
+    <row r="97" spans="1:3">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="B97" s="1">
+      <c r="B97" s="2">
         <v>5932269677</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="2">
         <v>3966215411</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="2">
+    <row r="98" spans="1:3">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="1">
+      <c r="B98" s="2">
         <v>5307839437</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="2">
         <v>2890447416</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="2">
+    <row r="99" spans="1:3">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="1">
+      <c r="B99" s="2">
         <v>5664344909</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99" s="2">
         <v>3773260652</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="2">
+    <row r="100" spans="1:3">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="B100" s="1">
+      <c r="B100" s="2">
         <v>7439247611</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="2">
         <v>6359600004</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="2">
+    <row r="101" spans="1:3">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="1">
+      <c r="B101" s="2">
         <v>2134702147</v>
       </c>
-      <c r="C101" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="2">
+      <c r="C101" s="3">
+        <v>0.258722097</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B102" s="2">
         <v>6501274722</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102" s="2">
         <v>4374832318</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="2">
+    <row r="103" spans="1:3">
+      <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="B103" s="1">
+      <c r="B103" s="2">
         <v>3651183174</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C103" s="2">
         <v>2155843323</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="2">
+    <row r="104" spans="1:3">
+      <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="B104" s="1">
+      <c r="B104" s="2">
         <v>2286495392</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104" s="2">
         <v>189355686</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="2">
+    <row r="105" spans="1:3">
+      <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="B105" s="1">
+      <c r="B105" s="2">
         <v>4748859137</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C105" s="2">
         <v>4902991575</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="2">
+    <row r="106" spans="1:3">
+      <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="B106" s="1">
+      <c r="B106" s="2">
         <v>5459160761</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="2">
         <v>4833506427</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="2">
+    <row r="107" spans="1:3">
+      <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="2">
         <v>3433064765</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107" s="2">
         <v>3172299463</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="2">
+    <row r="108" spans="1:3">
+      <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="2">
         <v>7176399653</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C108" s="2">
         <v>5029951665</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="2">
+    <row r="109" spans="1:3">
+      <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="2">
         <v>5506395117</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C109" s="2">
         <v>4261013003</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="2">
+    <row r="110" spans="1:3">
+      <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="2">
         <v>3097615732</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110" s="2">
         <v>167239058</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="2">
+    <row r="111" spans="1:3">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="2">
         <v>4647555992</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111" s="2">
         <v>1497024128</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" s="2">
+    <row r="112" spans="1:3">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="2">
         <v>1828306344</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112" s="2">
         <v>1345488916</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="2">
+    <row r="113" spans="1:3">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="2">
         <v>3534566235</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C113" s="2">
         <v>2667465435</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="2">
+    <row r="114" spans="1:3">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="2">
         <v>460617584</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114" s="2">
         <v>1999325527</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="2">
+    <row r="115" spans="1:3">
+      <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="2">
         <v>5361503134</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115" s="2">
         <v>5231863313</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="2">
+    <row r="116" spans="1:3">
+      <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="2">
         <v>6879333037</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116" s="2">
         <v>521140132</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="2">
+    <row r="117" spans="1:3">
+      <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="2">
         <v>4317032306</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117" s="2">
         <v>3661656456</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="2">
+    <row r="118" spans="1:3">
+      <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="2">
         <v>338316358</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118" s="2">
         <v>1415034656</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="2">
+    <row r="119" spans="1:3">
+      <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119" s="2">
         <v>4932207232</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119" s="2">
         <v>4933044092</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" s="2">
+    <row r="120" spans="1:3">
+      <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120" s="2">
         <v>4935596519</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C120" s="2">
         <v>4130778265</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="2">
+    <row r="121" spans="1:3">
+      <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="2">
         <v>2601553311</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C121" s="2">
         <v>2282266934</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="2">
+    <row r="122" spans="1:3">
+      <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122" s="2">
         <v>5711263543</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C122" s="2">
         <v>3901170334</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="2">
+    <row r="123" spans="1:3">
+      <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123" s="2">
         <v>6117530552</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C123" s="2">
         <v>4651998851</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="2">
+    <row r="124" spans="1:3">
+      <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="2">
         <v>3771415149</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C124" s="2">
         <v>3577800675</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="2">
+    <row r="125" spans="1:3">
+      <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125" s="2">
         <v>711722011</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C125" s="2">
         <v>5562545475</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" s="2">
+    <row r="126" spans="1:3">
+      <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="B126" s="1">
+      <c r="B126" s="2">
         <v>2194881851</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126" s="2">
         <v>239322812</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="2">
+    <row r="127" spans="1:3">
+      <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="B127" s="1">
+      <c r="B127" s="2">
         <v>5952001916</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="2">
         <v>356472374</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" s="2">
+    <row r="128" spans="1:3">
+      <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="B128" s="1">
+      <c r="B128" s="2">
         <v>3922302763</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="2">
         <v>2253721516</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="2">
+    <row r="129" spans="1:3">
+      <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="B129" s="1">
+      <c r="B129" s="2">
         <v>7081589058</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129" s="2">
         <v>4121647747</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="2">
+    <row r="130" spans="1:3">
+      <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="B130" s="1">
+      <c r="B130" s="2">
         <v>6950744997</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130" s="2">
         <v>4169100759</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" s="2">
+    <row r="131" spans="1:3">
+      <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="1">
+      <c r="B131" s="2">
         <v>3660876547</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131" s="2">
         <v>3823898686</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" s="2">
+    <row r="132" spans="1:3">
+      <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="B132" s="1">
+      <c r="B132" s="2">
         <v>178909178</v>
       </c>
-      <c r="C132" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="2">
+      <c r="C132" s="3">
+        <v>0.458377574</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="B133" s="1">
+      <c r="B133" s="2">
         <v>3540341099</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C133" s="2">
         <v>2576939959</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" s="2">
+    <row r="134" spans="1:3">
+      <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="B134" s="1">
+      <c r="B134" s="2">
         <v>4533395191</v>
       </c>
-      <c r="C134" s="1">
+      <c r="C134" s="2">
         <v>2947531471</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" s="2">
+    <row r="135" spans="1:3">
+      <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="B135" s="1">
+      <c r="B135" s="2">
         <v>4867339442</v>
       </c>
-      <c r="C135" s="1">
+      <c r="C135" s="2">
         <v>3739995796</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" s="2">
+    <row r="136" spans="1:3">
+      <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="B136" s="1">
+      <c r="B136" s="2">
         <v>4056005444</v>
       </c>
-      <c r="C136" s="1">
+      <c r="C136" s="2">
         <v>3571446511</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" s="2">
+    <row r="137" spans="1:3">
+      <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="B137" s="1">
+      <c r="B137" s="2">
         <v>5634643477</v>
       </c>
-      <c r="C137" s="1">
+      <c r="C137" s="2">
         <v>4808150425</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" s="2">
+    <row r="138" spans="1:3">
+      <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="B138" s="1">
+      <c r="B138" s="2">
         <v>5461635882</v>
       </c>
-      <c r="C138" s="1">
+      <c r="C138" s="2">
         <v>4017611208</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" s="2">
+    <row r="139" spans="1:3">
+      <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="B139" s="1">
+      <c r="B139" s="2">
         <v>3186175826</v>
       </c>
-      <c r="C139" s="1">
+      <c r="C139" s="2">
         <v>1839802006</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="2">
+    <row r="140" spans="1:3">
+      <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="B140" s="1">
+      <c r="B140" s="2">
         <v>4417665557</v>
       </c>
-      <c r="C140" s="1">
+      <c r="C140" s="2">
         <v>3468573793</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="2">
+    <row r="141" spans="1:3">
+      <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="B141" s="1">
+      <c r="B141" s="2">
         <v>5760289224</v>
       </c>
-      <c r="C141" s="1">
+      <c r="C141" s="2">
         <v>4658785492</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" s="2">
+    <row r="142" spans="1:3">
+      <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="B142" s="1">
+      <c r="B142" s="2">
         <v>3716700249</v>
       </c>
-      <c r="C142" s="1">
+      <c r="C142" s="2">
         <v>2391677519</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" s="2">
+    <row r="143" spans="1:3">
+      <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="B143" s="1">
+      <c r="B143" s="2">
         <v>2182561567</v>
       </c>
-      <c r="C143" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" s="2">
+      <c r="C143" s="3">
+        <v>0.992917365</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="B144" s="1">
+      <c r="B144" s="2">
         <v>429198369</v>
       </c>
-      <c r="C144" s="1">
+      <c r="C144" s="2">
         <v>316938024</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" s="2">
+    <row r="145" spans="1:3">
+      <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="B145" s="1">
+      <c r="B145" s="2">
         <v>3410030276</v>
       </c>
-      <c r="C145" s="1">
+      <c r="C145" s="2">
         <v>2089042355</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146" s="2">
+    <row r="146" spans="1:3">
+      <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="B146" s="1">
+      <c r="B146" s="2">
         <v>3581097036</v>
       </c>
-      <c r="C146" s="1">
+      <c r="C146" s="2">
         <v>1843675775</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147" s="2">
+    <row r="147" spans="1:3">
+      <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="1">
+      <c r="B147" s="2">
         <v>3509663093</v>
       </c>
-      <c r="C147" s="1">
+      <c r="C147" s="2">
         <v>1616607435</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" s="2">
+    <row r="148" spans="1:3">
+      <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="B148" s="1">
+      <c r="B148" s="2">
         <v>6660216364</v>
       </c>
-      <c r="C148" s="1">
+      <c r="C148" s="2">
         <v>5949347502</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" s="2">
+    <row r="149" spans="1:3">
+      <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="B149" s="1">
+      <c r="B149" s="2">
         <v>627178643</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C149" s="2">
         <v>4940227777</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" s="2">
+    <row r="150" spans="1:3">
+      <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="B150" s="1">
+      <c r="B150" s="2">
         <v>3735017626</v>
       </c>
-      <c r="C150" s="1">
+      <c r="C150" s="2">
         <v>2841238677</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151" s="2">
+    <row r="151" spans="1:3">
+      <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="B151" s="1">
+      <c r="B151" s="2">
         <v>439320834</v>
       </c>
-      <c r="C151" s="1">
+      <c r="C151" s="2">
         <v>2944391335</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" s="2">
+    <row r="152" spans="1:3">
+      <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="B152" s="1">
+      <c r="B152" s="2">
         <v>3512216897</v>
       </c>
-      <c r="C152" s="1">
+      <c r="C152" s="2">
         <v>3026918175</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" s="2">
+    <row r="153" spans="1:3">
+      <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="B153" s="1">
+      <c r="B153" s="2">
         <v>6239739633</v>
       </c>
-      <c r="C153" s="1">
+      <c r="C153" s="2">
         <v>5067802509</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" s="2">
+    <row r="154" spans="1:3">
+      <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="B154" s="1">
+      <c r="B154" s="2">
         <v>3681485586</v>
       </c>
-      <c r="C154" s="1">
+      <c r="C154" s="2">
         <v>3036819937</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" s="2">
+    <row r="155" spans="1:3">
+      <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="B155" s="1">
+      <c r="B155" s="2">
         <v>7241312999</v>
       </c>
-      <c r="C155" s="1">
+      <c r="C155" s="2">
         <v>468281699</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" s="2">
+    <row r="156" spans="1:3">
+      <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="B156" s="1">
+      <c r="B156" s="2">
         <v>6345369732</v>
       </c>
-      <c r="C156" s="1">
+      <c r="C156" s="2">
         <v>4000819183</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" s="2">
+    <row r="157" spans="1:3">
+      <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="B157" s="1">
+      <c r="B157" s="2">
         <v>5939741524</v>
       </c>
-      <c r="C157" s="1">
+      <c r="C157" s="2">
         <v>4570801127</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" s="2">
+    <row r="158" spans="1:3">
+      <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="B158" s="1">
+      <c r="B158" s="2">
         <v>245932138</v>
       </c>
-      <c r="C158" s="1">
+      <c r="C158" s="2">
         <v>2042739312</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159" s="2">
+    <row r="159" spans="1:3">
+      <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="B159" s="1">
+      <c r="B159" s="2">
         <v>2539088891</v>
       </c>
-      <c r="C159" s="1">
+      <c r="C159" s="2">
         <v>1748651124</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" s="2">
+    <row r="160" spans="1:3">
+      <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="B160" s="1">
+      <c r="B160" s="2">
         <v>6708603726</v>
       </c>
-      <c r="C160" s="1">
+      <c r="C160" s="2">
         <v>6064013048</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" s="2">
+    <row r="161" spans="1:3">
+      <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="B161" s="1">
+      <c r="B161" s="2">
         <v>6831322325</v>
       </c>
-      <c r="C161" s="1">
+      <c r="C161" s="2">
         <v>5132401469</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" s="2">
+    <row r="162" spans="1:3">
+      <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="B162" s="1">
+      <c r="B162" s="2">
         <v>5082657925</v>
       </c>
-      <c r="C162" s="1">
+      <c r="C162" s="2">
         <v>311334209</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A163" s="2">
+    <row r="163" spans="1:3">
+      <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="B163" s="1">
+      <c r="B163" s="2">
         <v>6030607372</v>
       </c>
-      <c r="C163" s="1">
+      <c r="C163" s="2">
         <v>4821810262</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" s="2">
+    <row r="164" spans="1:3">
+      <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="B164" s="1">
+      <c r="B164" s="2">
         <v>6574595032</v>
       </c>
-      <c r="C164" s="1">
+      <c r="C164" s="2">
         <v>4179521023</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A165" s="2">
+    <row r="165" spans="1:3">
+      <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="B165" s="1">
+      <c r="B165" s="2">
         <v>3574296929</v>
       </c>
-      <c r="C165" s="1">
+      <c r="C165" s="2">
         <v>1631261107</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" s="2">
+    <row r="166" spans="1:3">
+      <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="B166" s="1">
+      <c r="B166" s="2">
         <v>5529908432</v>
       </c>
-      <c r="C166" s="1">
+      <c r="C166" s="2">
         <v>3822179643</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167" s="2">
+    <row r="167" spans="1:3">
+      <c r="A167" s="1">
         <v>166</v>
       </c>
-      <c r="B167" s="1">
+      <c r="B167" s="2">
         <v>2409381746</v>
       </c>
-      <c r="C167" s="1">
+      <c r="C167" s="2">
         <v>1857541886</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" s="2">
+    <row r="168" spans="1:3">
+      <c r="A168" s="1">
         <v>167</v>
       </c>
-      <c r="B168" s="1">
+      <c r="B168" s="2">
         <v>4264789552</v>
       </c>
-      <c r="C168" s="1">
+      <c r="C168" s="2">
         <v>3751089281</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169" s="2">
+    <row r="169" spans="1:3">
+      <c r="A169" s="1">
         <v>168</v>
       </c>
-      <c r="B169" s="1">
+      <c r="B169" s="2">
         <v>3530344828</v>
       </c>
-      <c r="C169" s="1">
+      <c r="C169" s="2">
         <v>3158618594</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" s="2">
+    <row r="170" spans="1:3">
+      <c r="A170" s="1">
         <v>169</v>
       </c>
-      <c r="B170" s="1">
+      <c r="B170" s="2">
         <v>6143149816</v>
       </c>
-      <c r="C170" s="1">
+      <c r="C170" s="2">
         <v>4927132625</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A171" s="2">
+    <row r="171" spans="1:3">
+      <c r="A171" s="1">
         <v>170</v>
       </c>
-      <c r="B171" s="1">
+      <c r="B171" s="2">
         <v>5157697377</v>
       </c>
-      <c r="C171" s="1">
+      <c r="C171" s="2">
         <v>4600114757</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A172" s="2">
+    <row r="172" spans="1:3">
+      <c r="A172" s="1">
         <v>171</v>
       </c>
-      <c r="B172" s="1">
+      <c r="B172" s="2">
         <v>4710847457</v>
       </c>
-      <c r="C172" s="1">
+      <c r="C172" s="2">
         <v>2408379902</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173" s="2">
+    <row r="173" spans="1:3">
+      <c r="A173" s="1">
         <v>172</v>
       </c>
-      <c r="B173" s="1">
+      <c r="B173" s="2">
         <v>6847515267</v>
       </c>
-      <c r="C173" s="1">
+      <c r="C173" s="2">
         <v>4486703665</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174" s="2">
+    <row r="174" spans="1:3">
+      <c r="A174" s="1">
         <v>173</v>
       </c>
-      <c r="B174" s="1">
+      <c r="B174" s="2">
         <v>5464640093</v>
       </c>
-      <c r="C174" s="1">
+      <c r="C174" s="2">
         <v>2727715712</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" s="2">
+    <row r="175" spans="1:3">
+      <c r="A175" s="1">
         <v>174</v>
       </c>
-      <c r="B175" s="1">
+      <c r="B175" s="2">
         <v>4176532342</v>
       </c>
-      <c r="C175" s="1">
+      <c r="C175" s="2">
         <v>3020724447</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" s="2">
+    <row r="176" spans="1:3">
+      <c r="A176" s="1">
         <v>175</v>
       </c>
-      <c r="B176" s="1">
+      <c r="B176" s="2">
         <v>3748093215</v>
       </c>
-      <c r="C176" s="1">
+      <c r="C176" s="2">
         <v>3749180727</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" s="2">
+    <row r="177" spans="1:3">
+      <c r="A177" s="1">
         <v>176</v>
       </c>
-      <c r="B177" s="1">
+      <c r="B177" s="2">
         <v>2274523114</v>
       </c>
-      <c r="C177" s="1">
+      <c r="C177" s="2">
         <v>2311554237</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" s="2">
+    <row r="178" spans="1:3">
+      <c r="A178" s="1">
         <v>177</v>
       </c>
-      <c r="B178" s="1">
+      <c r="B178" s="2">
         <v>1576365722</v>
       </c>
-      <c r="C178" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" s="2">
+      <c r="C178" s="3">
+        <v>0.987603172</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="1">
         <v>178</v>
       </c>
-      <c r="B179" s="1">
+      <c r="B179" s="2">
         <v>1924133698</v>
       </c>
-      <c r="C179" s="1">
+      <c r="C179" s="2">
         <v>1461144421</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" s="2">
+    <row r="180" spans="1:3">
+      <c r="A180" s="1">
         <v>179</v>
       </c>
-      <c r="B180" s="1">
+      <c r="B180" s="2">
         <v>5904246043</v>
       </c>
-      <c r="C180" s="1">
+      <c r="C180" s="2">
         <v>457685653</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" s="2">
+    <row r="181" spans="1:3">
+      <c r="A181" s="1">
         <v>180</v>
       </c>
-      <c r="B181" s="1">
+      <c r="B181" s="2">
         <v>5189031076</v>
       </c>
-      <c r="C181" s="1">
+      <c r="C181" s="2">
         <v>4767595639</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" s="2">
+    <row r="182" spans="1:3">
+      <c r="A182" s="1">
         <v>181</v>
       </c>
-      <c r="B182" s="1">
+      <c r="B182" s="2">
         <v>187986818</v>
       </c>
-      <c r="C182" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" s="2">
+      <c r="C182" s="3">
+        <v>0.438171567</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="1">
         <v>182</v>
       </c>
-      <c r="B183" s="1">
+      <c r="B183" s="2">
         <v>2544347646</v>
       </c>
-      <c r="C183" s="1">
+      <c r="C183" s="2">
         <v>2351202468</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" s="2">
+    <row r="184" spans="1:3">
+      <c r="A184" s="1">
         <v>183</v>
       </c>
-      <c r="B184" s="1">
+      <c r="B184" s="2">
         <v>3221393614</v>
       </c>
-      <c r="C184" s="1">
+      <c r="C184" s="2">
         <v>3453102739</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" s="2">
+    <row r="185" spans="1:3">
+      <c r="A185" s="1">
         <v>184</v>
       </c>
-      <c r="B185" s="1">
+      <c r="B185" s="2">
         <v>7260374143</v>
       </c>
-      <c r="C185" s="1">
+      <c r="C185" s="2">
         <v>5381398471</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" s="2">
+    <row r="186" spans="1:3">
+      <c r="A186" s="1">
         <v>185</v>
       </c>
-      <c r="B186" s="1">
+      <c r="B186" s="2">
         <v>6481616962</v>
       </c>
-      <c r="C186" s="1">
+      <c r="C186" s="2">
         <v>4820091247</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187" s="2">
+    <row r="187" spans="1:3">
+      <c r="A187" s="1">
         <v>186</v>
       </c>
-      <c r="B187" s="1">
+      <c r="B187" s="2">
         <v>5688487723</v>
       </c>
-      <c r="C187" s="1">
+      <c r="C187" s="2">
         <v>4658742683</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" s="2">
+    <row r="188" spans="1:3">
+      <c r="A188" s="1">
         <v>187</v>
       </c>
-      <c r="B188" s="1">
+      <c r="B188" s="2">
         <v>6633618821</v>
       </c>
-      <c r="C188" s="1">
+      <c r="C188" s="2">
         <v>5380070207</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189" s="2">
+    <row r="189" spans="1:3">
+      <c r="A189" s="1">
         <v>188</v>
       </c>
-      <c r="B189" s="1">
+      <c r="B189" s="2">
         <v>5972741351</v>
       </c>
-      <c r="C189" s="1">
+      <c r="C189" s="2">
         <v>3315989476</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" s="2">
+    <row r="190" spans="1:3">
+      <c r="A190" s="1">
         <v>189</v>
       </c>
-      <c r="B190" s="1">
+      <c r="B190" s="2">
         <v>3897737917</v>
       </c>
-      <c r="C190" s="1">
+      <c r="C190" s="2">
         <v>2799747487</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A191" s="2">
+    <row r="191" spans="1:3">
+      <c r="A191" s="1">
         <v>190</v>
       </c>
-      <c r="B191" s="1">
+      <c r="B191" s="2">
         <v>6461243321</v>
       </c>
-      <c r="C191" s="1">
+      <c r="C191" s="2">
         <v>4206754912</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" s="2">
+    <row r="192" spans="1:3">
+      <c r="A192" s="1">
         <v>191</v>
       </c>
-      <c r="B192" s="1">
+      <c r="B192" s="2">
         <v>6628036302</v>
       </c>
-      <c r="C192" s="1">
+      <c r="C192" s="2">
         <v>4402663195</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193" s="2">
+    <row r="193" spans="1:3">
+      <c r="A193" s="1">
         <v>192</v>
       </c>
-      <c r="B193" s="1">
+      <c r="B193" s="2">
         <v>3118959195</v>
       </c>
-      <c r="C193" s="1">
+      <c r="C193" s="2">
         <v>2769118126</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" s="2">
+    <row r="194" spans="1:3">
+      <c r="A194" s="1">
         <v>193</v>
       </c>
-      <c r="B194" s="1">
+      <c r="B194" s="2">
         <v>4695963614</v>
       </c>
-      <c r="C194" s="1">
+      <c r="C194" s="2">
         <v>2784244545</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195" s="2">
+    <row r="195" spans="1:3">
+      <c r="A195" s="1">
         <v>194</v>
       </c>
-      <c r="B195" s="1">
+      <c r="B195" s="2">
         <v>1573693715</v>
       </c>
-      <c r="C195" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" s="2">
+      <c r="C195" s="3">
+        <v>0.688090581</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="1">
         <v>195</v>
       </c>
-      <c r="B196" s="1">
+      <c r="B196" s="2">
         <v>3670376931</v>
       </c>
-      <c r="C196" s="1">
+      <c r="C196" s="2">
         <v>347649914</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197" s="2">
+    <row r="197" spans="1:3">
+      <c r="A197" s="1">
         <v>196</v>
       </c>
-      <c r="B197" s="1">
+      <c r="B197" s="2">
         <v>719440696</v>
       </c>
-      <c r="C197" s="1">
+      <c r="C197" s="2">
         <v>5836196656</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" s="2">
+    <row r="198" spans="1:3">
+      <c r="A198" s="1">
         <v>197</v>
       </c>
-      <c r="B198" s="1">
+      <c r="B198" s="2">
         <v>1780478658</v>
       </c>
-      <c r="C198" s="1">
+      <c r="C198" s="2">
         <v>2003926093</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199" s="2">
+    <row r="199" spans="1:3">
+      <c r="A199" s="1">
         <v>198</v>
       </c>
-      <c r="B199" s="1">
+      <c r="B199" s="2">
         <v>2142359555</v>
       </c>
-      <c r="C199" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" s="2">
+      <c r="C199" s="3">
+        <v>0.971332454</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="1">
         <v>199</v>
       </c>
-      <c r="B200" s="1">
+      <c r="B200" s="2">
         <v>365648599</v>
       </c>
-      <c r="C200" s="1">
+      <c r="C200" s="2">
         <v>2857614364</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201" s="2">
+    <row r="201" spans="1:3">
+      <c r="A201" s="1">
         <v>200</v>
       </c>
-      <c r="B201" s="1">
+      <c r="B201" s="2">
         <v>2090354141</v>
       </c>
-      <c r="C201" s="1">
+      <c r="C201" s="2">
         <v>1852117711</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" s="2">
+    <row r="202" spans="1:3">
+      <c r="A202" s="1">
         <v>201</v>
       </c>
-      <c r="B202" s="1">
+      <c r="B202" s="2">
         <v>3363097172</v>
       </c>
-      <c r="C202" s="1">
+      <c r="C202" s="2">
         <v>3515179177</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203" s="2">
+    <row r="203" spans="1:3">
+      <c r="A203" s="1">
         <v>202</v>
       </c>
-      <c r="B203" s="1">
+      <c r="B203" s="2">
         <v>2423143852</v>
       </c>
-      <c r="C203" s="1">
+      <c r="C203" s="2">
         <v>2100552494</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" s="2">
+    <row r="204" spans="1:3">
+      <c r="A204" s="1">
         <v>203</v>
       </c>
-      <c r="B204" s="1">
+      <c r="B204" s="2">
         <v>7111583642</v>
       </c>
-      <c r="C204" s="1">
+      <c r="C204" s="2">
         <v>6086478284</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205" s="2">
+    <row r="205" spans="1:3">
+      <c r="A205" s="1">
         <v>204</v>
       </c>
-      <c r="B205" s="1">
+      <c r="B205" s="2">
         <v>3039941856</v>
       </c>
-      <c r="C205" s="1">
+      <c r="C205" s="2">
         <v>4083821161</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" s="2">
+    <row r="206" spans="1:3">
+      <c r="A206" s="1">
         <v>205</v>
       </c>
-      <c r="B206" s="1">
+      <c r="B206" s="2">
         <v>2373232035</v>
       </c>
-      <c r="C206" s="1">
+      <c r="C206" s="2">
         <v>1524782291</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" s="2">
+    <row r="207" spans="1:3">
+      <c r="A207" s="1">
         <v>206</v>
       </c>
-      <c r="B207" s="1">
+      <c r="B207" s="2">
         <v>198456369</v>
       </c>
-      <c r="C207" s="1">
+      <c r="C207" s="2">
         <v>2579516515</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" s="2">
+    <row r="208" spans="1:3">
+      <c r="A208" s="1">
         <v>207</v>
       </c>
-      <c r="B208" s="1">
+      <c r="B208" s="2">
         <v>2628482853</v>
       </c>
-      <c r="C208" s="1">
+      <c r="C208" s="2">
         <v>1619226127</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A209" s="2">
+    <row r="209" spans="1:3">
+      <c r="A209" s="1">
         <v>208</v>
       </c>
-      <c r="B209" s="1">
+      <c r="B209" s="2">
         <v>7136759971</v>
       </c>
-      <c r="C209" s="1">
+      <c r="C209" s="2">
         <v>5506621537</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210" s="2">
+    <row r="210" spans="1:3">
+      <c r="A210" s="1">
         <v>209</v>
       </c>
-      <c r="B210" s="1">
+      <c r="B210" s="2">
         <v>3104918354</v>
       </c>
-      <c r="C210" s="1">
+      <c r="C210" s="2">
         <v>1095999271</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A211" s="2">
+    <row r="211" spans="1:3">
+      <c r="A211" s="1">
         <v>210</v>
       </c>
-      <c r="B211" s="1">
+      <c r="B211" s="2">
         <v>1558656751</v>
       </c>
-      <c r="C211" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212" s="2">
+      <c r="C211" s="3">
+        <v>0.968527327</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" s="1">
         <v>211</v>
       </c>
-      <c r="B212" s="1">
+      <c r="B212" s="2">
         <v>7478446618</v>
       </c>
-      <c r="C212" s="1">
+      <c r="C212" s="2">
         <v>4877725538</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A213" s="2">
+    <row r="213" spans="1:3">
+      <c r="A213" s="1">
         <v>212</v>
       </c>
-      <c r="B213" s="1">
+      <c r="B213" s="2">
         <v>2813900047</v>
       </c>
-      <c r="C213" s="1">
+      <c r="C213" s="2">
         <v>1759698667</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214" s="2">
+    <row r="214" spans="1:3">
+      <c r="A214" s="1">
         <v>213</v>
       </c>
-      <c r="B214" s="1">
+      <c r="B214" s="2">
         <v>5744539644</v>
       </c>
-      <c r="C214" s="1">
+      <c r="C214" s="2">
         <v>5032211034</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A215" s="2">
+    <row r="215" spans="1:3">
+      <c r="A215" s="1">
         <v>214</v>
       </c>
-      <c r="B215" s="1">
+      <c r="B215" s="2">
         <v>6540988357</v>
       </c>
-      <c r="C215" s="1">
+      <c r="C215" s="2">
         <v>5713802294</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216" s="2">
+    <row r="216" spans="1:3">
+      <c r="A216" s="1">
         <v>215</v>
       </c>
-      <c r="B216" s="1">
+      <c r="B216" s="2">
         <v>6562794132</v>
       </c>
-      <c r="C216" s="1">
+      <c r="C216" s="2">
         <v>4795842867</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A217" s="2">
+    <row r="217" spans="1:3">
+      <c r="A217" s="1">
         <v>216</v>
       </c>
-      <c r="B217" s="1">
+      <c r="B217" s="2">
         <v>5470124995</v>
       </c>
-      <c r="C217" s="1">
+      <c r="C217" s="2">
         <v>4660289961</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218" s="2">
+    <row r="218" spans="1:3">
+      <c r="A218" s="1">
         <v>217</v>
       </c>
-      <c r="B218" s="1">
+      <c r="B218" s="2">
         <v>2085130525</v>
       </c>
-      <c r="C218" s="1">
+      <c r="C218" s="2">
         <v>2740395407</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A219" s="2">
+    <row r="219" spans="1:3">
+      <c r="A219" s="1">
         <v>218</v>
       </c>
-      <c r="B219" s="1">
+      <c r="B219" s="2">
         <v>4589572497</v>
       </c>
-      <c r="C219" s="1">
+      <c r="C219" s="2">
         <v>4250568064</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A220" s="2">
+    <row r="220" spans="1:3">
+      <c r="A220" s="1">
         <v>219</v>
       </c>
-      <c r="B220" s="1">
+      <c r="B220" s="2">
         <v>5074501769</v>
       </c>
-      <c r="C220" s="1">
+      <c r="C220" s="2">
         <v>3941019322</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A221" s="2">
+    <row r="221" spans="1:3">
+      <c r="A221" s="1">
         <v>220</v>
       </c>
-      <c r="B221" s="1">
+      <c r="B221" s="2">
         <v>7463509813</v>
       </c>
-      <c r="C221" s="1">
+      <c r="C221" s="2">
         <v>450344538</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A222" s="2">
+    <row r="222" spans="1:3">
+      <c r="A222" s="1">
         <v>221</v>
       </c>
-      <c r="B222" s="1">
+      <c r="B222" s="2">
         <v>5853905763</v>
       </c>
-      <c r="C222" s="1">
+      <c r="C222" s="2">
         <v>4633228732</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A223" s="2">
+    <row r="223" spans="1:3">
+      <c r="A223" s="1">
         <v>222</v>
       </c>
-      <c r="B223" s="1">
+      <c r="B223" s="2">
         <v>3764539962</v>
       </c>
-      <c r="C223" s="1">
+      <c r="C223" s="2">
         <v>4030864938</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A224" s="2">
+    <row r="224" spans="1:3">
+      <c r="A224" s="1">
         <v>223</v>
       </c>
-      <c r="B224" s="1">
+      <c r="B224" s="2">
         <v>706279211</v>
       </c>
-      <c r="C224" s="1">
+      <c r="C224" s="2">
         <v>6863387951</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A225" s="2">
+    <row r="225" spans="1:3">
+      <c r="A225" s="1">
         <v>224</v>
       </c>
-      <c r="B225" s="1">
+      <c r="B225" s="2">
         <v>6377376426</v>
       </c>
-      <c r="C225" s="1">
+      <c r="C225" s="2">
         <v>5079475899</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A226" s="2">
+    <row r="226" spans="1:3">
+      <c r="A226" s="1">
         <v>225</v>
       </c>
-      <c r="B226" s="1">
+      <c r="B226" s="2">
         <v>1920862764</v>
       </c>
-      <c r="C226" s="1">
+      <c r="C226" s="2">
         <v>1625268393</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A227" s="2">
+    <row r="227" spans="1:3">
+      <c r="A227" s="1">
         <v>226</v>
       </c>
-      <c r="B227" s="1">
+      <c r="B227" s="2">
         <v>7364213378</v>
       </c>
-      <c r="C227" s="1">
+      <c r="C227" s="2">
         <v>6618279842</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A228" s="2">
+    <row r="228" spans="1:3">
+      <c r="A228" s="1">
         <v>227</v>
       </c>
-      <c r="B228" s="1">
+      <c r="B228" s="2">
         <v>6535798861</v>
       </c>
-      <c r="C228" s="1">
+      <c r="C228" s="2">
         <v>4656998572</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229" s="2">
+    <row r="229" spans="1:3">
+      <c r="A229" s="1">
         <v>228</v>
       </c>
-      <c r="B229" s="1">
+      <c r="B229" s="2">
         <v>7300902725</v>
       </c>
-      <c r="C229" s="1">
+      <c r="C229" s="2">
         <v>6004987475</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A230" s="2">
+    <row r="230" spans="1:3">
+      <c r="A230" s="1">
         <v>229</v>
       </c>
-      <c r="B230" s="1">
+      <c r="B230" s="2">
         <v>3037231724</v>
       </c>
-      <c r="C230" s="1">
+      <c r="C230" s="2">
         <v>2410635566</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231" s="2">
+    <row r="231" spans="1:3">
+      <c r="A231" s="1">
         <v>230</v>
       </c>
-      <c r="B231" s="1">
+      <c r="B231" s="2">
         <v>6703266827</v>
       </c>
-      <c r="C231" s="1">
+      <c r="C231" s="2">
         <v>4261219972</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A232" s="2">
+    <row r="232" spans="1:3">
+      <c r="A232" s="1">
         <v>231</v>
       </c>
-      <c r="B232" s="1">
+      <c r="B232" s="2">
         <v>1927996684</v>
       </c>
-      <c r="C232" s="1">
+      <c r="C232" s="2">
         <v>1065623809</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A233" s="2">
+    <row r="233" spans="1:3">
+      <c r="A233" s="1">
         <v>232</v>
       </c>
-      <c r="B233" s="1">
+      <c r="B233" s="2">
         <v>4223553578</v>
       </c>
-      <c r="C233" s="1">
+      <c r="C233" s="2">
         <v>2295700142</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A234" s="2">
+    <row r="234" spans="1:3">
+      <c r="A234" s="1">
         <v>233</v>
       </c>
-      <c r="B234" s="1">
+      <c r="B234" s="2">
         <v>292270632</v>
       </c>
-      <c r="C234" s="1">
+      <c r="C234" s="2">
         <v>1919511103</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A235" s="2">
+    <row r="235" spans="1:3">
+      <c r="A235" s="1">
         <v>234</v>
       </c>
-      <c r="B235" s="1">
+      <c r="B235" s="2">
         <v>4427108605</v>
       </c>
-      <c r="C235" s="1">
+      <c r="C235" s="2">
         <v>3581381038</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A236" s="2">
+    <row r="236" spans="1:3">
+      <c r="A236" s="1">
         <v>235</v>
       </c>
-      <c r="B236" s="1">
+      <c r="B236" s="2">
         <v>207056241</v>
       </c>
-      <c r="C236" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A237" s="2">
+      <c r="C236" s="3">
+        <v>0.628942061</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" s="1">
         <v>236</v>
       </c>
-      <c r="B237" s="1">
+      <c r="B237" s="2">
         <v>5224070229</v>
       </c>
-      <c r="C237" s="1">
+      <c r="C237" s="2">
         <v>3344108372</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A238" s="2">
+    <row r="238" spans="1:3">
+      <c r="A238" s="1">
         <v>237</v>
       </c>
-      <c r="B238" s="1">
+      <c r="B238" s="2">
         <v>7161872875</v>
       </c>
-      <c r="C238" s="1">
+      <c r="C238" s="2">
         <v>6160434101</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A239" s="2">
+    <row r="239" spans="1:3">
+      <c r="A239" s="1">
         <v>238</v>
       </c>
-      <c r="B239" s="1">
+      <c r="B239" s="2">
         <v>2210696478</v>
       </c>
-      <c r="C239" s="1">
+      <c r="C239" s="2">
         <v>2861274444</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A240" s="2">
+    <row r="240" spans="1:3">
+      <c r="A240" s="1">
         <v>239</v>
       </c>
-      <c r="B240" s="1">
+      <c r="B240" s="2">
         <v>72070597</v>
       </c>
-      <c r="C240" s="1">
+      <c r="C240" s="2">
         <v>4209470573</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A241" s="2">
+    <row r="241" spans="1:3">
+      <c r="A241" s="1">
         <v>240</v>
       </c>
-      <c r="B241" s="1">
+      <c r="B241" s="2">
         <v>2184084991</v>
       </c>
-      <c r="C241" s="1">
+      <c r="C241" s="2">
         <v>1226298134</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A242" s="2">
+    <row r="242" spans="1:3">
+      <c r="A242" s="1">
         <v>241</v>
       </c>
-      <c r="B242" s="1">
+      <c r="B242" s="2">
         <v>4414998466</v>
       </c>
-      <c r="C242" s="1">
+      <c r="C242" s="2">
         <v>479332516</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A243" s="2">
+    <row r="243" spans="1:3">
+      <c r="A243" s="1">
         <v>242</v>
       </c>
-      <c r="B243" s="1">
+      <c r="B243" s="2">
         <v>5014809669</v>
       </c>
-      <c r="C243" s="1">
+      <c r="C243" s="2">
         <v>3313796516</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A244" s="2">
+    <row r="244" spans="1:3">
+      <c r="A244" s="1">
         <v>243</v>
       </c>
-      <c r="B244" s="1">
+      <c r="B244" s="2">
         <v>260203712</v>
       </c>
-      <c r="C244" s="1">
+      <c r="C244" s="2">
         <v>2152698433</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A245" s="2">
+    <row r="245" spans="1:3">
+      <c r="A245" s="1">
         <v>244</v>
       </c>
-      <c r="B245" s="1">
+      <c r="B245" s="2">
         <v>2917048671</v>
       </c>
-      <c r="C245" s="1">
+      <c r="C245" s="2">
         <v>2923683874</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A246" s="2">
+    <row r="246" spans="1:3">
+      <c r="A246" s="1">
         <v>245</v>
       </c>
-      <c r="B246" s="1">
+      <c r="B246" s="2">
         <v>6244341635</v>
       </c>
-      <c r="C246" s="1">
+      <c r="C246" s="2">
         <v>3452067233</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A247" s="2">
+    <row r="247" spans="1:3">
+      <c r="A247" s="1">
         <v>246</v>
       </c>
-      <c r="B247" s="1">
+      <c r="B247" s="2">
         <v>6859654494</v>
       </c>
-      <c r="C247" s="1">
+      <c r="C247" s="2">
         <v>4258311529</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A248" s="2">
+    <row r="248" spans="1:3">
+      <c r="A248" s="1">
         <v>247</v>
       </c>
-      <c r="B248" s="1">
+      <c r="B248" s="2">
         <v>2371230424</v>
       </c>
-      <c r="C248" s="1">
+      <c r="C248" s="2">
         <v>3961032766</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A249" s="2">
+    <row r="249" spans="1:3">
+      <c r="A249" s="1">
         <v>248</v>
       </c>
-      <c r="B249" s="1">
+      <c r="B249" s="2">
         <v>596405759</v>
       </c>
-      <c r="C249" s="1">
+      <c r="C249" s="2">
         <v>3427723163</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A250" s="2">
+    <row r="250" spans="1:3">
+      <c r="A250" s="1">
         <v>249</v>
       </c>
-      <c r="B250" s="1">
+      <c r="B250" s="2">
         <v>7153674088</v>
       </c>
-      <c r="C250" s="1">
+      <c r="C250" s="2">
         <v>4720987338</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A251" s="2">
+    <row r="251" spans="1:3">
+      <c r="A251" s="1">
         <v>250</v>
       </c>
-      <c r="B251" s="1">
+      <c r="B251" s="2">
         <v>228989742</v>
       </c>
-      <c r="C251" s="1">
+      <c r="C251" s="2">
         <v>1571949813</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A252" s="2">
+    <row r="252" spans="1:3">
+      <c r="A252" s="1">
         <v>251</v>
       </c>
-      <c r="B252" s="1">
+      <c r="B252" s="2">
         <v>6376228033</v>
       </c>
-      <c r="C252" s="1">
+      <c r="C252" s="2">
         <v>6186945609</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A253" s="2">
+    <row r="253" spans="1:3">
+      <c r="A253" s="1">
         <v>252</v>
       </c>
-      <c r="B253" s="1">
+      <c r="B253" s="2">
         <v>3540504299</v>
       </c>
-      <c r="C253" s="1">
+      <c r="C253" s="2">
         <v>3552736964</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A254" s="2">
+    <row r="254" spans="1:3">
+      <c r="A254" s="1">
         <v>253</v>
       </c>
-      <c r="B254" s="1">
+      <c r="B254" s="2">
         <v>313982572</v>
       </c>
-      <c r="C254" s="1">
+      <c r="C254" s="2">
         <v>1245785944</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A255" s="2">
+    <row r="255" spans="1:3">
+      <c r="A255" s="1">
         <v>254</v>
       </c>
-      <c r="B255" s="1">
+      <c r="B255" s="2">
         <v>6460742301</v>
       </c>
-      <c r="C255" s="1">
+      <c r="C255" s="2">
         <v>3426911652</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A256" s="2">
+    <row r="256" spans="1:3">
+      <c r="A256" s="1">
         <v>255</v>
       </c>
-      <c r="B256" s="1">
+      <c r="B256" s="2">
         <v>2641348462</v>
       </c>
-      <c r="C256" s="1">
+      <c r="C256" s="2">
         <v>1877147043</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A257" s="2">
+    <row r="257" spans="1:3">
+      <c r="A257" s="1">
         <v>256</v>
       </c>
-      <c r="B257" s="1">
+      <c r="B257" s="2">
         <v>2002213553</v>
       </c>
-      <c r="C257" s="1">
+      <c r="C257" s="2">
         <v>1817889113</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A258" s="2">
+    <row r="258" spans="1:3">
+      <c r="A258" s="1">
         <v>257</v>
       </c>
-      <c r="B258" s="1">
+      <c r="B258" s="2">
         <v>6391428135</v>
       </c>
-      <c r="C258" s="1">
+      <c r="C258" s="2">
         <v>5239909498</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A259" s="2">
+    <row r="259" spans="1:3">
+      <c r="A259" s="1">
         <v>258</v>
       </c>
-      <c r="B259" s="1">
+      <c r="B259" s="2">
         <v>2763719772</v>
       </c>
-      <c r="C259" s="1">
+      <c r="C259" s="2">
         <v>1384044112</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A260" s="2">
+    <row r="260" spans="1:3">
+      <c r="A260" s="1">
         <v>259</v>
       </c>
-      <c r="B260" s="1">
+      <c r="B260" s="2">
         <v>6831257549</v>
       </c>
-      <c r="C260" s="1">
+      <c r="C260" s="2">
         <v>3837977768</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A261" s="2">
+    <row r="261" spans="1:3">
+      <c r="A261" s="1">
         <v>260</v>
       </c>
-      <c r="B261" s="1">
+      <c r="B261" s="2">
         <v>3827254525</v>
       </c>
-      <c r="C261" s="1">
+      <c r="C261" s="2">
         <v>232169769</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A262" s="2">
+    <row r="262" spans="1:3">
+      <c r="A262" s="1">
         <v>261</v>
       </c>
-      <c r="B262" s="1">
+      <c r="B262" s="2">
         <v>3770670898</v>
       </c>
-      <c r="C262" s="1">
+      <c r="C262" s="2">
         <v>331157823</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A263" s="2">
+    <row r="263" spans="1:3">
+      <c r="A263" s="1">
         <v>262</v>
       </c>
-      <c r="B263" s="1">
+      <c r="B263" s="2">
         <v>3159854892</v>
       </c>
-      <c r="C263" s="1">
+      <c r="C263" s="2">
         <v>305738784</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A264" s="2">
+    <row r="264" spans="1:3">
+      <c r="A264" s="1">
         <v>263</v>
       </c>
-      <c r="B264" s="1">
+      <c r="B264" s="2">
         <v>5099417157</v>
       </c>
-      <c r="C264" s="1">
+      <c r="C264" s="2">
         <v>4737045954</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A265" s="2">
+    <row r="265" spans="1:3">
+      <c r="A265" s="1">
         <v>264</v>
       </c>
-      <c r="B265" s="1">
+      <c r="B265" s="2">
         <v>5610390825</v>
       </c>
-      <c r="C265" s="1">
+      <c r="C265" s="2">
         <v>4590970461</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A266" s="2">
+    <row r="266" spans="1:3">
+      <c r="A266" s="1">
         <v>265</v>
       </c>
-      <c r="B266" s="1">
+      <c r="B266" s="2">
         <v>1856371752</v>
       </c>
-      <c r="C266" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A267" s="2">
+      <c r="C266" s="3">
+        <v>0.654242148</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="1">
         <v>266</v>
       </c>
-      <c r="B267" s="1">
+      <c r="B267" s="2">
         <v>5363729581</v>
       </c>
-      <c r="C267" s="1">
+      <c r="C267" s="2">
         <v>3981127739</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A268" s="2">
+    <row r="268" spans="1:3">
+      <c r="A268" s="1">
         <v>267</v>
       </c>
-      <c r="B268" s="1">
+      <c r="B268" s="2">
         <v>2366133563</v>
       </c>
-      <c r="C268" s="1">
+      <c r="C268" s="2">
         <v>2336276033</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A269" s="2">
+    <row r="269" spans="1:3">
+      <c r="A269" s="1">
         <v>268</v>
       </c>
-      <c r="B269" s="1">
+      <c r="B269" s="2">
         <v>4975851368</v>
       </c>
-      <c r="C269" s="1">
+      <c r="C269" s="2">
         <v>4540636147</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A270" s="2">
+    <row r="270" spans="1:3">
+      <c r="A270" s="1">
         <v>269</v>
       </c>
-      <c r="B270" s="1">
+      <c r="B270" s="2">
         <v>2665954677</v>
       </c>
-      <c r="C270" s="1">
+      <c r="C270" s="2">
         <v>2192744863</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A271" s="2">
+    <row r="271" spans="1:3">
+      <c r="A271" s="1">
         <v>270</v>
       </c>
-      <c r="B271" s="1">
+      <c r="B271" s="2">
         <v>2646458097</v>
       </c>
-      <c r="C271" s="1">
+      <c r="C271" s="2">
         <v>1788176341</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A272" s="2">
+    <row r="272" spans="1:3">
+      <c r="A272" s="1">
         <v>271</v>
       </c>
-      <c r="B272" s="1">
+      <c r="B272" s="2">
         <v>3859892387</v>
       </c>
-      <c r="C272" s="1">
+      <c r="C272" s="2">
         <v>271943218</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A273" s="2">
+    <row r="273" spans="1:3">
+      <c r="A273" s="1">
         <v>272</v>
       </c>
-      <c r="B273" s="1">
+      <c r="B273" s="2">
         <v>4121530621</v>
       </c>
-      <c r="C273" s="1">
+      <c r="C273" s="2">
         <v>4212697339</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A274" s="2">
+    <row r="274" spans="1:3">
+      <c r="A274" s="1">
         <v>273</v>
       </c>
-      <c r="B274" s="1">
+      <c r="B274" s="2">
         <v>638594064</v>
       </c>
-      <c r="C274" s="1">
+      <c r="C274" s="2">
         <v>4477271392</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A275" s="2">
+    <row r="275" spans="1:3">
+      <c r="A275" s="1">
         <v>274</v>
       </c>
-      <c r="B275" s="1">
+      <c r="B275" s="2">
         <v>3842709679</v>
       </c>
-      <c r="C275" s="1">
+      <c r="C275" s="2">
         <v>2468859994</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A276" s="2">
+    <row r="276" spans="1:3">
+      <c r="A276" s="1">
         <v>275</v>
       </c>
-      <c r="B276" s="1">
+      <c r="B276" s="2">
         <v>4990548538</v>
       </c>
-      <c r="C276" s="1">
+      <c r="C276" s="2">
         <v>3451772538</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A277" s="2">
+    <row r="277" spans="1:3">
+      <c r="A277" s="1">
         <v>276</v>
       </c>
-      <c r="B277" s="1">
+      <c r="B277" s="2">
         <v>3400596941</v>
       </c>
-      <c r="C277" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A278" s="2">
+      <c r="C277" s="3">
+        <v>0.686920849</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="1">
         <v>277</v>
       </c>
-      <c r="B278" s="1">
+      <c r="B278" s="2">
         <v>3820115372</v>
       </c>
-      <c r="C278" s="1">
+      <c r="C278" s="2">
         <v>2246745707</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A279" s="2">
+    <row r="279" spans="1:3">
+      <c r="A279" s="1">
         <v>278</v>
       </c>
-      <c r="B279" s="1">
+      <c r="B279" s="2">
         <v>1909499153</v>
       </c>
-      <c r="C279" s="1">
+      <c r="C279" s="2">
         <v>1627695089</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A280" s="2">
+    <row r="280" spans="1:3">
+      <c r="A280" s="1">
         <v>279</v>
       </c>
-      <c r="B280" s="1">
+      <c r="B280" s="2">
         <v>2858464123</v>
       </c>
-      <c r="C280" s="1">
+      <c r="C280" s="2">
         <v>2453209061</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A281" s="2">
+    <row r="281" spans="1:3">
+      <c r="A281" s="1">
         <v>280</v>
       </c>
-      <c r="B281" s="1">
+      <c r="B281" s="2">
         <v>745150065</v>
       </c>
-      <c r="C281" s="1">
+      <c r="C281" s="2">
         <v>4109944653</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A282" s="2">
+    <row r="282" spans="1:3">
+      <c r="A282" s="1">
         <v>281</v>
       </c>
-      <c r="B282" s="1">
+      <c r="B282" s="2">
         <v>3354252107</v>
       </c>
-      <c r="C282" s="1">
+      <c r="C282" s="2">
         <v>2572598203</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A283" s="2">
+    <row r="283" spans="1:3">
+      <c r="A283" s="1">
         <v>282</v>
       </c>
-      <c r="B283" s="1">
+      <c r="B283" s="2">
         <v>6707825202</v>
       </c>
-      <c r="C283" s="1">
+      <c r="C283" s="2">
         <v>4810424058</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A284" s="2">
+    <row r="284" spans="1:3">
+      <c r="A284" s="1">
         <v>283</v>
       </c>
-      <c r="B284" s="1">
+      <c r="B284" s="2">
         <v>6325906067</v>
       </c>
-      <c r="C284" s="1">
+      <c r="C284" s="2">
         <v>4827416304</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A285" s="2">
+    <row r="285" spans="1:3">
+      <c r="A285" s="1">
         <v>284</v>
       </c>
-      <c r="B285" s="1">
+      <c r="B285" s="2">
         <v>1931180677</v>
       </c>
-      <c r="C285" s="1">
+      <c r="C285" s="2">
         <v>2465761128</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A286" s="2">
+    <row r="286" spans="1:3">
+      <c r="A286" s="1">
         <v>285</v>
       </c>
-      <c r="B286" s="1">
+      <c r="B286" s="2">
         <v>5128545227</v>
       </c>
-      <c r="C286" s="1">
+      <c r="C286" s="2">
         <v>3757378987</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A287" s="2">
+    <row r="287" spans="1:3">
+      <c r="A287" s="1">
         <v>286</v>
       </c>
-      <c r="B287" s="1">
+      <c r="B287" s="2">
         <v>4278209872</v>
       </c>
-      <c r="C287" s="1">
+      <c r="C287" s="2">
         <v>3691348189</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A288" s="2">
+    <row r="288" spans="1:3">
+      <c r="A288" s="1">
         <v>287</v>
       </c>
-      <c r="B288" s="1">
+      <c r="B288" s="2">
         <v>1579470288</v>
       </c>
-      <c r="C288" s="1">
+      <c r="C288" s="2">
         <v>1981809911</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A289" s="2">
+    <row r="289" spans="1:3">
+      <c r="A289" s="1">
         <v>288</v>
       </c>
-      <c r="B289" s="1">
+      <c r="B289" s="2">
         <v>2907682177</v>
       </c>
-      <c r="C289" s="1">
+      <c r="C289" s="2">
         <v>1410229567</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A290" s="2">
+    <row r="290" spans="1:3">
+      <c r="A290" s="1">
         <v>289</v>
       </c>
-      <c r="B290" s="1">
+      <c r="B290" s="2">
         <v>556471409</v>
       </c>
-      <c r="C290" s="1">
+      <c r="C290" s="2">
         <v>375430142</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A291" s="2">
+    <row r="291" spans="1:3">
+      <c r="A291" s="1">
         <v>290</v>
       </c>
-      <c r="B291" s="1">
+      <c r="B291" s="2">
         <v>3571175436</v>
       </c>
-      <c r="C291" s="1">
+      <c r="C291" s="2">
         <v>4245215597</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A292" s="2">
+    <row r="292" spans="1:3">
+      <c r="A292" s="1">
         <v>291</v>
       </c>
-      <c r="B292" s="1">
+      <c r="B292" s="2">
         <v>2345107567</v>
       </c>
-      <c r="C292" s="1">
+      <c r="C292" s="2">
         <v>1437876724</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A293" s="2">
+    <row r="293" spans="1:3">
+      <c r="A293" s="1">
         <v>292</v>
       </c>
-      <c r="B293" s="1">
+      <c r="B293" s="2">
         <v>5845197028</v>
       </c>
-      <c r="C293" s="1">
+      <c r="C293" s="2">
         <v>4159887144</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A294" s="2">
+    <row r="294" spans="1:3">
+      <c r="A294" s="1">
         <v>293</v>
       </c>
-      <c r="B294" s="1">
+      <c r="B294" s="2">
         <v>5298480408</v>
       </c>
-      <c r="C294" s="1">
+      <c r="C294" s="2">
         <v>3514891782</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A295" s="2">
+    <row r="295" spans="1:3">
+      <c r="A295" s="1">
         <v>294</v>
       </c>
-      <c r="B295" s="1">
+      <c r="B295" s="2">
         <v>3434699925</v>
       </c>
-      <c r="C295" s="1">
+      <c r="C295" s="2">
         <v>2714498038</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A296" s="2">
+    <row r="296" spans="1:3">
+      <c r="A296" s="1">
         <v>295</v>
       </c>
-      <c r="B296" s="1">
+      <c r="B296" s="2">
         <v>1865995232</v>
       </c>
-      <c r="C296" s="1">
+      <c r="C296" s="2">
         <v>1357373136</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A297" s="2">
+    <row r="297" spans="1:3">
+      <c r="A297" s="1">
         <v>296</v>
       </c>
-      <c r="B297" s="1">
+      <c r="B297" s="2">
         <v>5095615491</v>
       </c>
-      <c r="C297" s="1">
+      <c r="C297" s="2">
         <v>5638460387</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A298" s="2">
+    <row r="298" spans="1:3">
+      <c r="A298" s="1">
         <v>297</v>
       </c>
-      <c r="B298" s="1">
+      <c r="B298" s="2">
         <v>1530807727</v>
       </c>
-      <c r="C298" s="1">
+      <c r="C298" s="2">
         <v>2421464669</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A299" s="2">
+    <row r="299" spans="1:3">
+      <c r="A299" s="1">
         <v>298</v>
       </c>
-      <c r="B299" s="1">
+      <c r="B299" s="2">
         <v>1618311459</v>
       </c>
-      <c r="C299" s="1">
+      <c r="C299" s="2">
         <v>1511205108</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A300" s="2">
+    <row r="300" spans="1:3">
+      <c r="A300" s="1">
         <v>299</v>
       </c>
-      <c r="B300" s="1">
+      <c r="B300" s="2">
         <v>6687677218</v>
       </c>
-      <c r="C300" s="1">
+      <c r="C300" s="2">
         <v>5522891668</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A301" s="2">
+    <row r="301" spans="1:3">
+      <c r="A301" s="1">
         <v>300</v>
       </c>
-      <c r="B301" s="1">
+      <c r="B301" s="2">
         <v>7347245523</v>
       </c>
-      <c r="C301" s="1">
+      <c r="C301" s="2">
         <v>4396622319</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A302" s="2">
+    <row r="302" spans="1:3">
+      <c r="A302" s="1">
         <v>301</v>
       </c>
-      <c r="B302" s="1">
+      <c r="B302" s="2">
         <v>5983845696</v>
       </c>
-      <c r="C302" s="1">
+      <c r="C302" s="2">
         <v>3988452835</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A303" s="2">
+    <row r="303" spans="1:3">
+      <c r="A303" s="1">
         <v>302</v>
       </c>
-      <c r="B303" s="1">
+      <c r="B303" s="2">
         <v>5196082373</v>
       </c>
-      <c r="C303" s="1">
+      <c r="C303" s="2">
         <v>331760678</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A304" s="2">
+    <row r="304" spans="1:3">
+      <c r="A304" s="1">
         <v>303</v>
       </c>
-      <c r="B304" s="1">
+      <c r="B304" s="2">
         <v>4193007431</v>
       </c>
-      <c r="C304" s="1">
+      <c r="C304" s="2">
         <v>2779682627</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A305" s="2">
+    <row r="305" spans="1:3">
+      <c r="A305" s="1">
         <v>304</v>
       </c>
-      <c r="B305" s="1">
+      <c r="B305" s="2">
         <v>2347687551</v>
       </c>
-      <c r="C305" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A306" s="2">
+      <c r="C305" s="3">
+        <v>0.846505526</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" s="1">
         <v>305</v>
       </c>
-      <c r="B306" s="1">
+      <c r="B306" s="2">
         <v>4709489378</v>
       </c>
-      <c r="C306" s="1">
+      <c r="C306" s="2">
         <v>2457921707</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A307" s="2">
+    <row r="307" spans="1:3">
+      <c r="A307" s="1">
         <v>306</v>
       </c>
-      <c r="B307" s="1">
+      <c r="B307" s="2">
         <v>230719771</v>
       </c>
-      <c r="C307" s="1">
+      <c r="C307" s="2">
         <v>3509604688</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A308" s="2">
+    <row r="308" spans="1:3">
+      <c r="A308" s="1">
         <v>307</v>
       </c>
-      <c r="B308" s="1">
+      <c r="B308" s="2">
         <v>2730768821</v>
       </c>
-      <c r="C308" s="1">
+      <c r="C308" s="2">
         <v>2646904537</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A309" s="2">
+    <row r="309" spans="1:3">
+      <c r="A309" s="1">
         <v>308</v>
       </c>
-      <c r="B309" s="1">
+      <c r="B309" s="2">
         <v>3782513505</v>
       </c>
-      <c r="C309" s="1">
+      <c r="C309" s="2">
         <v>2977916724</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A310" s="2">
+    <row r="310" spans="1:3">
+      <c r="A310" s="1">
         <v>309</v>
       </c>
-      <c r="B310" s="1">
+      <c r="B310" s="2">
         <v>3574393645</v>
       </c>
-      <c r="C310" s="1">
+      <c r="C310" s="2">
         <v>1424450548</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A311" s="2">
+    <row r="311" spans="1:3">
+      <c r="A311" s="1">
         <v>310</v>
       </c>
-      <c r="B311" s="1">
+      <c r="B311" s="2">
         <v>4159576384</v>
       </c>
-      <c r="C311" s="1">
+      <c r="C311" s="2">
         <v>1790342317</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A312" s="2">
+    <row r="312" spans="1:3">
+      <c r="A312" s="1">
         <v>311</v>
       </c>
-      <c r="B312" s="1">
+      <c r="B312" s="2">
         <v>1544634333</v>
       </c>
-      <c r="C312" s="1">
+      <c r="C312" s="2">
         <v>1644636603</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A313" s="2">
+    <row r="313" spans="1:3">
+      <c r="A313" s="1">
         <v>312</v>
       </c>
-      <c r="B313" s="1">
+      <c r="B313" s="2">
         <v>3383896674</v>
       </c>
-      <c r="C313" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A314" s="2">
+      <c r="C313" s="3">
+        <v>0.73163629</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" s="1">
         <v>313</v>
       </c>
-      <c r="B314" s="1">
+      <c r="B314" s="2">
         <v>3614745183</v>
       </c>
-      <c r="C314" s="1">
+      <c r="C314" s="2">
         <v>2901788592</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A315" s="2">
+    <row r="315" spans="1:3">
+      <c r="A315" s="1">
         <v>314</v>
       </c>
-      <c r="B315" s="1">
+      <c r="B315" s="2">
         <v>6503882324</v>
       </c>
-      <c r="C315" s="1">
+      <c r="C315" s="2">
         <v>4317133158</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A316" s="2">
+    <row r="316" spans="1:3">
+      <c r="A316" s="1">
         <v>315</v>
       </c>
-      <c r="B316" s="1">
+      <c r="B316" s="2">
         <v>1768412558</v>
       </c>
-      <c r="C316" s="1">
+      <c r="C316" s="2">
         <v>209736906</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A317" s="2">
+    <row r="317" spans="1:3">
+      <c r="A317" s="1">
         <v>316</v>
       </c>
-      <c r="B317" s="1">
+      <c r="B317" s="2">
         <v>4420311904</v>
       </c>
-      <c r="C317" s="1">
+      <c r="C317" s="2">
         <v>4391592976</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A318" s="2">
+    <row r="318" spans="1:3">
+      <c r="A318" s="1">
         <v>317</v>
       </c>
-      <c r="B318" s="1">
+      <c r="B318" s="2">
         <v>6477153237</v>
       </c>
-      <c r="C318" s="1">
+      <c r="C318" s="2">
         <v>5313956903</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A319" s="2">
+    <row r="319" spans="1:3">
+      <c r="A319" s="1">
         <v>318</v>
       </c>
-      <c r="B319" s="1">
+      <c r="B319" s="2">
         <v>6561419985</v>
       </c>
-      <c r="C319" s="1">
+      <c r="C319" s="2">
         <v>6281370191</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A320" s="2">
+    <row r="320" spans="1:3">
+      <c r="A320" s="1">
         <v>319</v>
       </c>
-      <c r="B320" s="1">
+      <c r="B320" s="2">
         <v>7180907194</v>
       </c>
-      <c r="C320" s="1">
+      <c r="C320" s="2">
         <v>560796663</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A321" s="2">
+    <row r="321" spans="1:3">
+      <c r="A321" s="1">
         <v>320</v>
       </c>
-      <c r="B321" s="1">
+      <c r="B321" s="2">
         <v>2809090781</v>
       </c>
-      <c r="C321" s="1">
+      <c r="C321" s="2">
         <v>2946870435</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A322" s="2">
+    <row r="322" spans="1:3">
+      <c r="A322" s="1">
         <v>321</v>
       </c>
-      <c r="B322" s="1">
+      <c r="B322" s="2">
         <v>568620541</v>
       </c>
-      <c r="C322" s="1">
+      <c r="C322" s="2">
         <v>3872788848</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A323" s="2">
+    <row r="323" spans="1:3">
+      <c r="A323" s="1">
         <v>322</v>
       </c>
-      <c r="B323" s="1">
+      <c r="B323" s="2">
         <v>4800343746</v>
       </c>
-      <c r="C323" s="1">
+      <c r="C323" s="2">
         <v>2842868351</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A324" s="2">
+    <row r="324" spans="1:3">
+      <c r="A324" s="1">
         <v>323</v>
       </c>
-      <c r="B324" s="1">
+      <c r="B324" s="2">
         <v>2412912159</v>
       </c>
-      <c r="C324" s="1">
+      <c r="C324" s="2">
         <v>146061633</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A325" s="2">
+    <row r="325" spans="1:3">
+      <c r="A325" s="1">
         <v>324</v>
       </c>
-      <c r="B325" s="1">
+      <c r="B325" s="2">
         <v>292570352</v>
       </c>
-      <c r="C325" s="1">
+      <c r="C325" s="2">
         <v>3752824766</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A326" s="2">
+    <row r="326" spans="1:3">
+      <c r="A326" s="1">
         <v>325</v>
       </c>
-      <c r="B326" s="1">
+      <c r="B326" s="2">
         <v>3174175764</v>
       </c>
-      <c r="C326" s="1">
+      <c r="C326" s="2">
         <v>3126603239</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A327" s="2">
+    <row r="327" spans="1:3">
+      <c r="A327" s="1">
         <v>326</v>
       </c>
-      <c r="B327" s="1">
+      <c r="B327" s="2">
         <v>2685529629</v>
       </c>
-      <c r="C327" s="1">
+      <c r="C327" s="2">
         <v>2821192645</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A328" s="2">
+    <row r="328" spans="1:3">
+      <c r="A328" s="1">
         <v>327</v>
       </c>
-      <c r="B328" s="1">
+      <c r="B328" s="2">
         <v>2124429242</v>
       </c>
-      <c r="C328" s="1">
+      <c r="C328" s="2">
         <v>2734960056</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A329" s="2">
+    <row r="329" spans="1:3">
+      <c r="A329" s="1">
         <v>328</v>
       </c>
-      <c r="B329" s="1">
+      <c r="B329" s="2">
         <v>2694022127</v>
       </c>
-      <c r="C329" s="1">
+      <c r="C329" s="2">
         <v>219759212</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A330" s="2">
+    <row r="330" spans="1:3">
+      <c r="A330" s="1">
         <v>329</v>
       </c>
-      <c r="B330" s="1">
+      <c r="B330" s="2">
         <v>4230888794</v>
       </c>
-      <c r="C330" s="1">
+      <c r="C330" s="2">
         <v>4155540864</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A331" s="2">
+    <row r="331" spans="1:3">
+      <c r="A331" s="1">
         <v>330</v>
       </c>
-      <c r="B331" s="1">
+      <c r="B331" s="2">
         <v>5350515664</v>
       </c>
-      <c r="C331" s="1">
+      <c r="C331" s="2">
         <v>4078208838</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A332" s="2">
+    <row r="332" spans="1:3">
+      <c r="A332" s="1">
         <v>331</v>
       </c>
-      <c r="B332" s="1">
+      <c r="B332" s="2">
         <v>5091579506</v>
       </c>
-      <c r="C332" s="1">
+      <c r="C332" s="2">
         <v>445696361</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A333" s="2">
+    <row r="333" spans="1:3">
+      <c r="A333" s="1">
         <v>332</v>
       </c>
-      <c r="B333" s="1">
+      <c r="B333" s="2">
         <v>6250302214</v>
       </c>
-      <c r="C333" s="1">
+      <c r="C333" s="2">
         <v>493925896</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A334" s="2">
+    <row r="334" spans="1:3">
+      <c r="A334" s="1">
         <v>333</v>
       </c>
-      <c r="B334" s="1">
+      <c r="B334" s="2">
         <v>5324632561</v>
       </c>
-      <c r="C334" s="1">
+      <c r="C334" s="2">
         <v>3730569958</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A335" s="2">
+    <row r="335" spans="1:3">
+      <c r="A335" s="1">
         <v>334</v>
       </c>
-      <c r="B335" s="1">
+      <c r="B335" s="2">
         <v>2048497711</v>
       </c>
-      <c r="C335" s="1">
+      <c r="C335" s="2">
         <v>2575054857</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A336" s="2">
+    <row r="336" spans="1:3">
+      <c r="A336" s="1">
         <v>335</v>
       </c>
-      <c r="B336" s="1">
+      <c r="B336" s="2">
         <v>2381385245</v>
       </c>
-      <c r="C336" s="1">
+      <c r="C336" s="2">
         <v>2176322145</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A337" s="2">
+    <row r="337" spans="1:3">
+      <c r="A337" s="1">
         <v>336</v>
       </c>
-      <c r="B337" s="1">
+      <c r="B337" s="2">
         <v>6919942971</v>
       </c>
-      <c r="C337" s="1">
+      <c r="C337" s="2">
         <v>6236955312</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A338" s="2">
+    <row r="338" spans="1:3">
+      <c r="A338" s="1">
         <v>337</v>
       </c>
-      <c r="B338" s="1">
+      <c r="B338" s="2">
         <v>2359507794</v>
       </c>
-      <c r="C338" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A339" s="2">
+      <c r="C338" s="3">
+        <v>0.898732803</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="1">
         <v>338</v>
       </c>
-      <c r="B339" s="1">
+      <c r="B339" s="2">
         <v>4545707462</v>
       </c>
-      <c r="C339" s="1">
+      <c r="C339" s="2">
         <v>3629424387</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A340" s="2">
+    <row r="340" spans="1:3">
+      <c r="A340" s="1">
         <v>339</v>
       </c>
-      <c r="B340" s="1">
+      <c r="B340" s="2">
         <v>7310502636</v>
       </c>
-      <c r="C340" s="1">
+      <c r="C340" s="2">
         <v>5923346071</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A341" s="2">
+    <row r="341" spans="1:3">
+      <c r="A341" s="1">
         <v>340</v>
       </c>
-      <c r="B341" s="1">
+      <c r="B341" s="2">
         <v>1697463691</v>
       </c>
-      <c r="C341" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A342" s="2">
+      <c r="C341" s="3">
+        <v>0.546190176</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" s="1">
         <v>341</v>
       </c>
-      <c r="B342" s="1">
+      <c r="B342" s="2">
         <v>458358582</v>
       </c>
-      <c r="C342" s="1">
+      <c r="C342" s="2">
         <v>3031497066</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A343" s="2">
+    <row r="343" spans="1:3">
+      <c r="A343" s="1">
         <v>342</v>
       </c>
-      <c r="B343" s="1">
+      <c r="B343" s="2">
         <v>207995534</v>
       </c>
-      <c r="C343" s="1">
+      <c r="C343" s="2">
         <v>2847816843</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A344" s="2">
+    <row r="344" spans="1:3">
+      <c r="A344" s="1">
         <v>343</v>
       </c>
-      <c r="B344" s="1">
+      <c r="B344" s="2">
         <v>4834397386</v>
       </c>
-      <c r="C344" s="1">
+      <c r="C344" s="2">
         <v>451696059</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A345" s="2">
+    <row r="345" spans="1:3">
+      <c r="A345" s="1">
         <v>344</v>
       </c>
-      <c r="B345" s="1">
+      <c r="B345" s="2">
         <v>4761344479</v>
       </c>
-      <c r="C345" s="1">
+      <c r="C345" s="2">
         <v>459169701</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A346" s="2">
+    <row r="346" spans="1:3">
+      <c r="A346" s="1">
         <v>345</v>
       </c>
-      <c r="B346" s="1">
+      <c r="B346" s="2">
         <v>4470036551</v>
       </c>
-      <c r="C346" s="1">
+      <c r="C346" s="2">
         <v>3157765091</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A347" s="2">
+    <row r="347" spans="1:3">
+      <c r="A347" s="1">
         <v>346</v>
       </c>
-      <c r="B347" s="1">
+      <c r="B347" s="2">
         <v>5379795423</v>
       </c>
-      <c r="C347" s="1">
+      <c r="C347" s="2">
         <v>428799968</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A348" s="2">
+    <row r="348" spans="1:3">
+      <c r="A348" s="1">
         <v>347</v>
       </c>
-      <c r="B348" s="1">
+      <c r="B348" s="2">
         <v>4255557225</v>
       </c>
-      <c r="C348" s="1">
+      <c r="C348" s="2">
         <v>3618829789</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A349" s="2">
+    <row r="349" spans="1:3">
+      <c r="A349" s="1">
         <v>348</v>
       </c>
-      <c r="B349" s="1">
+      <c r="B349" s="2">
         <v>4216468481</v>
       </c>
-      <c r="C349" s="1">
+      <c r="C349" s="2">
         <v>320079786</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A350" s="2">
+    <row r="350" spans="1:3">
+      <c r="A350" s="1">
         <v>349</v>
       </c>
-      <c r="B350" s="1">
+      <c r="B350" s="2">
         <v>5693725061</v>
       </c>
-      <c r="C350" s="1">
+      <c r="C350" s="2">
         <v>3999703007</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A351" s="2">
+    <row r="351" spans="1:3">
+      <c r="A351" s="1">
         <v>350</v>
       </c>
-      <c r="B351" s="1">
+      <c r="B351" s="2">
         <v>2996520703</v>
       </c>
-      <c r="C351" s="1">
+      <c r="C351" s="2">
         <v>1662253199</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A352" s="2">
+    <row r="352" spans="1:3">
+      <c r="A352" s="1">
         <v>351</v>
       </c>
-      <c r="B352" s="1">
+      <c r="B352" s="2">
         <v>2849458214</v>
       </c>
-      <c r="C352" s="1">
+      <c r="C352" s="2">
         <v>2391549999</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A353" s="2">
+    <row r="353" spans="1:3">
+      <c r="A353" s="1">
         <v>352</v>
       </c>
-      <c r="B353" s="1">
+      <c r="B353" s="2">
         <v>3744973637</v>
       </c>
-      <c r="C353" s="1">
+      <c r="C353" s="2">
         <v>3067609453</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A354" s="2">
+    <row r="354" spans="1:3">
+      <c r="A354" s="1">
         <v>353</v>
       </c>
-      <c r="B354" s="1">
+      <c r="B354" s="2">
         <v>3441513288</v>
       </c>
-      <c r="C354" s="1">
+      <c r="C354" s="2">
         <v>2017513588</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A355" s="2">
+    <row r="355" spans="1:3">
+      <c r="A355" s="1">
         <v>354</v>
       </c>
-      <c r="B355" s="1">
+      <c r="B355" s="2">
         <v>428007538</v>
       </c>
-      <c r="C355" s="1">
+      <c r="C355" s="2">
         <v>364088397</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A356" s="2">
+    <row r="356" spans="1:3">
+      <c r="A356" s="1">
         <v>355</v>
       </c>
-      <c r="B356" s="1">
+      <c r="B356" s="2">
         <v>1824455719</v>
       </c>
-      <c r="C356" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A357" s="2">
+      <c r="C356" s="3">
+        <v>0.266043663</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" s="1">
         <v>356</v>
       </c>
-      <c r="B357" s="1">
+      <c r="B357" s="2">
         <v>2889242002</v>
       </c>
-      <c r="C357" s="1">
+      <c r="C357" s="2">
         <v>1295427294</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A358" s="2">
+    <row r="358" spans="1:3">
+      <c r="A358" s="1">
         <v>357</v>
       </c>
-      <c r="B358" s="1">
+      <c r="B358" s="2">
         <v>2169977498</v>
       </c>
-      <c r="C358" s="1">
+      <c r="C358" s="2">
         <v>1853347613</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A359" s="2">
+    <row r="359" spans="1:3">
+      <c r="A359" s="1">
         <v>358</v>
       </c>
-      <c r="B359" s="1">
+      <c r="B359" s="2">
         <v>69768987</v>
       </c>
-      <c r="C359" s="1">
+      <c r="C359" s="2">
         <v>5367236103</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A360" s="2">
+    <row r="360" spans="1:3">
+      <c r="A360" s="1">
         <v>359</v>
       </c>
-      <c r="B360" s="1">
+      <c r="B360" s="2">
         <v>2683731229</v>
       </c>
-      <c r="C360" s="1">
+      <c r="C360" s="2">
         <v>2466292344</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A361" s="2">
+    <row r="361" spans="1:3">
+      <c r="A361" s="1">
         <v>360</v>
       </c>
-      <c r="B361" s="1">
+      <c r="B361" s="2">
         <v>1651156092</v>
       </c>
-      <c r="C361" s="1">
+      <c r="C361" s="2">
         <v>1723593561</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A362" s="2">
+    <row r="362" spans="1:3">
+      <c r="A362" s="1">
         <v>361</v>
       </c>
-      <c r="B362" s="1">
+      <c r="B362" s="2">
         <v>4416320576</v>
       </c>
-      <c r="C362" s="1">
+      <c r="C362" s="2">
         <v>4307288416</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A363" s="2">
+    <row r="363" spans="1:3">
+      <c r="A363" s="1">
         <v>362</v>
       </c>
-      <c r="B363" s="1">
+      <c r="B363" s="2">
         <v>3881098692</v>
       </c>
-      <c r="C363" s="1">
+      <c r="C363" s="2">
         <v>3156367436</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A364" s="2">
+    <row r="364" spans="1:3">
+      <c r="A364" s="1">
         <v>363</v>
       </c>
-      <c r="B364" s="1">
+      <c r="B364" s="2">
         <v>3784560552</v>
       </c>
-      <c r="C364" s="1">
+      <c r="C364" s="2">
         <v>1690458095</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A365" s="2">
+    <row r="365" spans="1:3">
+      <c r="A365" s="1">
         <v>364</v>
       </c>
-      <c r="B365" s="1">
+      <c r="B365" s="2">
         <v>62672605</v>
       </c>
-      <c r="C365" s="1">
+      <c r="C365" s="2">
         <v>5085523011</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A366" s="2">
+    <row r="366" spans="1:3">
+      <c r="A366" s="1">
         <v>365</v>
       </c>
-      <c r="B366" s="1">
+      <c r="B366" s="2">
         <v>189032676</v>
       </c>
-      <c r="C366" s="1">
+      <c r="C366" s="2">
         <v>248162387</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A367" s="2">
+    <row r="367" spans="1:3">
+      <c r="A367" s="1">
         <v>366</v>
       </c>
-      <c r="B367" s="1">
+      <c r="B367" s="2">
         <v>1762058178</v>
       </c>
-      <c r="C367" s="1">
+      <c r="C367" s="2">
         <v>1353317341</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A368" s="2">
+    <row r="368" spans="1:3">
+      <c r="A368" s="1">
         <v>367</v>
       </c>
-      <c r="B368" s="1">
+      <c r="B368" s="2">
         <v>6089162512</v>
       </c>
-      <c r="C368" s="1">
+      <c r="C368" s="2">
         <v>5275294151</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A369" s="2">
+    <row r="369" spans="1:3">
+      <c r="A369" s="1">
         <v>368</v>
       </c>
-      <c r="B369" s="1">
+      <c r="B369" s="2">
         <v>6374253863</v>
       </c>
-      <c r="C369" s="1">
+      <c r="C369" s="2">
         <v>3670291526</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A370" s="2">
+    <row r="370" spans="1:3">
+      <c r="A370" s="1">
         <v>369</v>
       </c>
-      <c r="B370" s="1">
+      <c r="B370" s="2">
         <v>6392483125</v>
       </c>
-      <c r="C370" s="1">
+      <c r="C370" s="2">
         <v>369639041</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A371" s="2">
+    <row r="371" spans="1:3">
+      <c r="A371" s="1">
         <v>370</v>
       </c>
-      <c r="B371" s="1">
+      <c r="B371" s="2">
         <v>3204316343</v>
       </c>
-      <c r="C371" s="1">
+      <c r="C371" s="2">
         <v>2679887318</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A372" s="2">
+    <row r="372" spans="1:3">
+      <c r="A372" s="1">
         <v>371</v>
       </c>
-      <c r="B372" s="1">
+      <c r="B372" s="2">
         <v>2908146911</v>
       </c>
-      <c r="C372" s="1">
+      <c r="C372" s="2">
         <v>2363564669</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A373" s="2">
+    <row r="373" spans="1:3">
+      <c r="A373" s="1">
         <v>372</v>
       </c>
-      <c r="B373" s="1">
+      <c r="B373" s="2">
         <v>2349952069</v>
       </c>
-      <c r="C373" s="1">
+      <c r="C373" s="2">
         <v>1438596105</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A374" s="2">
+    <row r="374" spans="1:3">
+      <c r="A374" s="1">
         <v>373</v>
       </c>
-      <c r="B374" s="1">
+      <c r="B374" s="2">
         <v>7004398837</v>
       </c>
-      <c r="C374" s="1">
+      <c r="C374" s="2">
         <v>5362448263</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A375" s="2">
+    <row r="375" spans="1:3">
+      <c r="A375" s="1">
         <v>374</v>
       </c>
-      <c r="B375" s="1">
+      <c r="B375" s="2">
         <v>3483599117</v>
       </c>
-      <c r="C375" s="1">
+      <c r="C375" s="2">
         <v>2325309226</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A376" s="2">
+    <row r="376" spans="1:3">
+      <c r="A376" s="1">
         <v>375</v>
       </c>
-      <c r="B376" s="1">
+      <c r="B376" s="2">
         <v>2517463803</v>
       </c>
-      <c r="C376" s="1">
+      <c r="C376" s="2">
         <v>1529560944</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A377" s="2">
+    <row r="377" spans="1:3">
+      <c r="A377" s="1">
         <v>376</v>
       </c>
-      <c r="B377" s="1">
+      <c r="B377" s="2">
         <v>5698451341</v>
       </c>
-      <c r="C377" s="1">
+      <c r="C377" s="2">
         <v>4035727019</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A378" s="2">
+    <row r="378" spans="1:3">
+      <c r="A378" s="1">
         <v>377</v>
       </c>
-      <c r="B378" s="1">
+      <c r="B378" s="2">
         <v>4381923282</v>
       </c>
-      <c r="C378" s="1">
+      <c r="C378" s="2">
         <v>3550337184</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A379" s="2">
+    <row r="379" spans="1:3">
+      <c r="A379" s="1">
         <v>378</v>
       </c>
-      <c r="B379" s="1">
+      <c r="B379" s="2">
         <v>477205909</v>
       </c>
-      <c r="C379" s="1">
+      <c r="C379" s="2">
         <v>3554600317</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A380" s="2">
+    <row r="380" spans="1:3">
+      <c r="A380" s="1">
         <v>379</v>
       </c>
-      <c r="B380" s="1">
+      <c r="B380" s="2">
         <v>5395016451</v>
       </c>
-      <c r="C380" s="1">
+      <c r="C380" s="2">
         <v>4199728526</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A381" s="2">
+    <row r="381" spans="1:3">
+      <c r="A381" s="1">
         <v>380</v>
       </c>
-      <c r="B381" s="1">
+      <c r="B381" s="2">
         <v>5456441309</v>
       </c>
-      <c r="C381" s="1">
+      <c r="C381" s="2">
         <v>3135475154</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A382" s="2">
+    <row r="382" spans="1:3">
+      <c r="A382" s="1">
         <v>381</v>
       </c>
-      <c r="B382" s="1">
+      <c r="B382" s="2">
         <v>1788359923</v>
       </c>
-      <c r="C382" s="1">
+      <c r="C382" s="2">
         <v>1145295813</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A383" s="2">
+    <row r="383" spans="1:3">
+      <c r="A383" s="1">
         <v>382</v>
       </c>
-      <c r="B383" s="1">
+      <c r="B383" s="2">
         <v>3112592784</v>
       </c>
-      <c r="C383" s="1">
+      <c r="C383" s="2">
         <v>3539854127</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A384" s="2">
+    <row r="384" spans="1:3">
+      <c r="A384" s="1">
         <v>383</v>
       </c>
-      <c r="B384" s="1">
+      <c r="B384" s="2">
         <v>5080968448</v>
       </c>
-      <c r="C384" s="1">
+      <c r="C384" s="2">
         <v>3822203964</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A385" s="2">
+    <row r="385" spans="1:3">
+      <c r="A385" s="1">
         <v>384</v>
       </c>
-      <c r="B385" s="1">
+      <c r="B385" s="2">
         <v>4851313918</v>
       </c>
-      <c r="C385" s="1">
+      <c r="C385" s="2">
         <v>3835577646</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A386" s="2">
+    <row r="386" spans="1:3">
+      <c r="A386" s="1">
         <v>385</v>
       </c>
-      <c r="B386" s="1">
+      <c r="B386" s="2">
         <v>6607472112</v>
       </c>
-      <c r="C386" s="1">
+      <c r="C386" s="2">
         <v>5683750561</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A387" s="2">
+    <row r="387" spans="1:3">
+      <c r="A387" s="1">
         <v>386</v>
       </c>
-      <c r="B387" s="1">
+      <c r="B387" s="2">
         <v>3126856179</v>
       </c>
-      <c r="C387" s="1">
+      <c r="C387" s="2">
         <v>2517400876</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A388" s="2">
+    <row r="388" spans="1:3">
+      <c r="A388" s="1">
         <v>387</v>
       </c>
-      <c r="B388" s="1">
+      <c r="B388" s="2">
         <v>6562762833</v>
       </c>
-      <c r="C388" s="1">
+      <c r="C388" s="2">
         <v>4324660384</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A389" s="2">
+    <row r="389" spans="1:3">
+      <c r="A389" s="1">
         <v>388</v>
       </c>
-      <c r="B389" s="1">
+      <c r="B389" s="2">
         <v>2343075473</v>
       </c>
-      <c r="C389" s="1">
+      <c r="C389" s="2">
         <v>2958696801</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A390" s="2">
+    <row r="390" spans="1:3">
+      <c r="A390" s="1">
         <v>389</v>
       </c>
-      <c r="B390" s="1">
+      <c r="B390" s="2">
         <v>1600033017</v>
       </c>
-      <c r="C390" s="1">
+      <c r="C390" s="2">
         <v>1680997133</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A391" s="2">
+    <row r="391" spans="1:3">
+      <c r="A391" s="1">
         <v>390</v>
       </c>
-      <c r="B391" s="1">
+      <c r="B391" s="2">
         <v>5248175536</v>
       </c>
-      <c r="C391" s="1">
+      <c r="C391" s="2">
         <v>4253501304</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A392" s="2">
+    <row r="392" spans="1:3">
+      <c r="A392" s="1">
         <v>391</v>
       </c>
-      <c r="B392" s="1">
+      <c r="B392" s="2">
         <v>3035461316</v>
       </c>
-      <c r="C392" s="1">
+      <c r="C392" s="2">
         <v>2260395693</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A393" s="2">
+    <row r="393" spans="1:3">
+      <c r="A393" s="1">
         <v>392</v>
       </c>
-      <c r="B393" s="1">
+      <c r="B393" s="2">
         <v>4947372147</v>
       </c>
-      <c r="C393" s="1">
+      <c r="C393" s="2">
         <v>3615471053</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A394" s="2">
+    <row r="394" spans="1:3">
+      <c r="A394" s="1">
         <v>393</v>
       </c>
-      <c r="B394" s="1">
+      <c r="B394" s="2">
         <v>1574953616</v>
       </c>
-      <c r="C394" s="1">
+      <c r="C394" s="2">
         <v>1502211626</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A395" s="2">
+    <row r="395" spans="1:3">
+      <c r="A395" s="1">
         <v>394</v>
       </c>
-      <c r="B395" s="1">
+      <c r="B395" s="2">
         <v>5741724885</v>
       </c>
-      <c r="C395" s="1">
+      <c r="C395" s="2">
         <v>3776484631</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A396" s="2">
+    <row r="396" spans="1:3">
+      <c r="A396" s="1">
         <v>395</v>
       </c>
-      <c r="B396" s="1">
+      <c r="B396" s="2">
         <v>591047527</v>
       </c>
-      <c r="C396" s="1">
+      <c r="C396" s="2">
         <v>3201042435</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A397" s="2">
+    <row r="397" spans="1:3">
+      <c r="A397" s="1">
         <v>396</v>
       </c>
-      <c r="B397" s="1">
+      <c r="B397" s="2">
         <v>6195003987</v>
       </c>
-      <c r="C397" s="1">
+      <c r="C397" s="2">
         <v>4058311616</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A398" s="2">
+    <row r="398" spans="1:3">
+      <c r="A398" s="1">
         <v>397</v>
       </c>
-      <c r="B398" s="1">
+      <c r="B398" s="2">
         <v>5492589725</v>
       </c>
-      <c r="C398" s="1">
+      <c r="C398" s="2">
         <v>4105224517</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A399" s="2">
+    <row r="399" spans="1:3">
+      <c r="A399" s="1">
         <v>398</v>
       </c>
-      <c r="B399" s="1">
+      <c r="B399" s="2">
         <v>4517244574</v>
       </c>
-      <c r="C399" s="1">
+      <c r="C399" s="2">
         <v>3722097639</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A400" s="2">
+    <row r="400" spans="1:3">
+      <c r="A400" s="1">
         <v>399</v>
       </c>
-      <c r="B400" s="1">
+      <c r="B400" s="2">
         <v>4311785997</v>
       </c>
-      <c r="C400" s="1">
+      <c r="C400" s="2">
         <v>3822270313</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A401" s="2">
+    <row r="401" spans="1:3">
+      <c r="A401" s="1">
         <v>400</v>
       </c>
-      <c r="B401" s="1">
+      <c r="B401" s="2">
         <v>463374137</v>
       </c>
-      <c r="C401" s="1">
+      <c r="C401" s="2">
         <v>3706660981</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A402" s="2">
+    <row r="402" spans="1:3">
+      <c r="A402" s="1">
         <v>401</v>
       </c>
-      <c r="B402" s="1">
+      <c r="B402" s="2">
         <v>7423832498</v>
       </c>
-      <c r="C402" s="1">
+      <c r="C402" s="2">
         <v>4909688469</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A403" s="2">
+    <row r="403" spans="1:3">
+      <c r="A403" s="1">
         <v>402</v>
       </c>
-      <c r="B403" s="1">
+      <c r="B403" s="2">
         <v>2507768548</v>
       </c>
-      <c r="C403" s="1">
+      <c r="C403" s="2">
         <v>2155733626</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A404" s="2">
+    <row r="404" spans="1:3">
+      <c r="A404" s="1">
         <v>403</v>
       </c>
-      <c r="B404" s="1">
+      <c r="B404" s="2">
         <v>5712586659</v>
       </c>
-      <c r="C404" s="1">
+      <c r="C404" s="2">
         <v>5743736081</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A405" s="2">
+    <row r="405" spans="1:3">
+      <c r="A405" s="1">
         <v>404</v>
       </c>
-      <c r="B405" s="1">
+      <c r="B405" s="2">
         <v>682237691</v>
       </c>
-      <c r="C405" s="1">
+      <c r="C405" s="2">
         <v>4337571452</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A406" s="2">
+    <row r="406" spans="1:3">
+      <c r="A406" s="1">
         <v>405</v>
       </c>
-      <c r="B406" s="1">
+      <c r="B406" s="2">
         <v>3367591818</v>
       </c>
-      <c r="C406" s="1">
+      <c r="C406" s="2">
         <v>258241664</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A407" s="2">
+    <row r="407" spans="1:3">
+      <c r="A407" s="1">
         <v>406</v>
       </c>
-      <c r="B407" s="1">
+      <c r="B407" s="2">
         <v>6320191311</v>
       </c>
-      <c r="C407" s="1">
+      <c r="C407" s="2">
         <v>4284305558</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A408" s="2">
+    <row r="408" spans="1:3">
+      <c r="A408" s="1">
         <v>407</v>
       </c>
-      <c r="B408" s="1">
+      <c r="B408" s="2">
         <v>2298643365</v>
       </c>
-      <c r="C408" s="1">
+      <c r="C408" s="2">
         <v>296216821</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A409" s="2">
+    <row r="409" spans="1:3">
+      <c r="A409" s="1">
         <v>408</v>
       </c>
-      <c r="B409" s="1">
+      <c r="B409" s="2">
         <v>4699895879</v>
       </c>
-      <c r="C409" s="1">
+      <c r="C409" s="2">
         <v>3990415894</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A410" s="2">
+    <row r="410" spans="1:3">
+      <c r="A410" s="1">
         <v>409</v>
       </c>
-      <c r="B410" s="1">
+      <c r="B410" s="2">
         <v>7246754831</v>
       </c>
-      <c r="C410" s="1">
+      <c r="C410" s="2">
         <v>5890148697</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A411" s="2">
+    <row r="411" spans="1:3">
+      <c r="A411" s="1">
         <v>410</v>
       </c>
-      <c r="B411" s="1">
+      <c r="B411" s="2">
         <v>5666951153</v>
       </c>
-      <c r="C411" s="1">
+      <c r="C411" s="2">
         <v>3688539518</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A412" s="2">
+    <row r="412" spans="1:3">
+      <c r="A412" s="1">
         <v>411</v>
       </c>
-      <c r="B412" s="1">
+      <c r="B412" s="2">
         <v>4087461982</v>
       </c>
-      <c r="C412" s="1">
+      <c r="C412" s="2">
         <v>3217847363</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A413" s="2">
+    <row r="413" spans="1:3">
+      <c r="A413" s="1">
         <v>412</v>
       </c>
-      <c r="B413" s="1">
+      <c r="B413" s="2">
         <v>3314556071</v>
       </c>
-      <c r="C413" s="1">
+      <c r="C413" s="2">
         <v>2220470327</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A414" s="2">
+    <row r="414" spans="1:3">
+      <c r="A414" s="1">
         <v>413</v>
       </c>
-      <c r="B414" s="1">
+      <c r="B414" s="2">
         <v>6768336228</v>
       </c>
-      <c r="C414" s="1">
+      <c r="C414" s="2">
         <v>5910284878</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A415" s="2">
+    <row r="415" spans="1:3">
+      <c r="A415" s="1">
         <v>414</v>
       </c>
-      <c r="B415" s="1">
+      <c r="B415" s="2">
         <v>540574906</v>
       </c>
-      <c r="C415" s="1">
+      <c r="C415" s="2">
         <v>4853032519</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A416" s="2">
+    <row r="416" spans="1:3">
+      <c r="A416" s="1">
         <v>415</v>
       </c>
-      <c r="B416" s="1">
+      <c r="B416" s="2">
         <v>363228339</v>
       </c>
-      <c r="C416" s="1">
+      <c r="C416" s="2">
         <v>3802973633</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A417" s="2">
+    <row r="417" spans="1:3">
+      <c r="A417" s="1">
         <v>416</v>
       </c>
-      <c r="B417" s="1">
+      <c r="B417" s="2">
         <v>4924949687</v>
       </c>
-      <c r="C417" s="1">
+      <c r="C417" s="2">
         <v>3092164648</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A418" s="2">
+    <row r="418" spans="1:3">
+      <c r="A418" s="1">
         <v>417</v>
       </c>
-      <c r="B418" s="1">
+      <c r="B418" s="2">
         <v>3699205521</v>
       </c>
-      <c r="C418" s="1">
+      <c r="C418" s="2">
         <v>3233313747</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A419" s="2">
+    <row r="419" spans="1:3">
+      <c r="A419" s="1">
         <v>418</v>
       </c>
-      <c r="B419" s="1">
+      <c r="B419" s="2">
         <v>6896929289</v>
       </c>
-      <c r="C419" s="1">
+      <c r="C419" s="2">
         <v>5265478958</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A420" s="2">
+    <row r="420" spans="1:3">
+      <c r="A420" s="1">
         <v>419</v>
       </c>
-      <c r="B420" s="1">
+      <c r="B420" s="2">
         <v>7025517695</v>
       </c>
-      <c r="C420" s="1">
+      <c r="C420" s="2">
         <v>481153338</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A421" s="2">
+    <row r="421" spans="1:3">
+      <c r="A421" s="1">
         <v>420</v>
       </c>
-      <c r="B421" s="1">
+      <c r="B421" s="2">
         <v>6475625217</v>
       </c>
-      <c r="C421" s="1">
+      <c r="C421" s="2">
         <v>5368041173</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A422" s="2">
+    <row r="422" spans="1:3">
+      <c r="A422" s="1">
         <v>421</v>
       </c>
-      <c r="B422" s="1">
+      <c r="B422" s="2">
         <v>163938057</v>
       </c>
-      <c r="C422" s="1">
+      <c r="C422" s="2">
         <v>1798718303</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A423" s="2">
+    <row r="423" spans="1:3">
+      <c r="A423" s="1">
         <v>422</v>
       </c>
-      <c r="B423" s="1">
+      <c r="B423" s="2">
         <v>6635954116</v>
       </c>
-      <c r="C423" s="1">
+      <c r="C423" s="2">
         <v>4760014333</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A424" s="2">
+    <row r="424" spans="1:3">
+      <c r="A424" s="1">
         <v>423</v>
       </c>
-      <c r="B424" s="1">
+      <c r="B424" s="2">
         <v>4604409215</v>
       </c>
-      <c r="C424" s="1">
+      <c r="C424" s="2">
         <v>3415806479</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A425" s="2">
+    <row r="425" spans="1:3">
+      <c r="A425" s="1">
         <v>424</v>
       </c>
-      <c r="B425" s="1">
+      <c r="B425" s="2">
         <v>7032057099</v>
       </c>
-      <c r="C425" s="1">
+      <c r="C425" s="2">
         <v>5040174582</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A426" s="2">
+    <row r="426" spans="1:3">
+      <c r="A426" s="1">
         <v>425</v>
       </c>
-      <c r="B426" s="1">
+      <c r="B426" s="2">
         <v>3102346043</v>
       </c>
-      <c r="C426" s="1">
+      <c r="C426" s="2">
         <v>1965635933</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A427" s="2">
+    <row r="427" spans="1:3">
+      <c r="A427" s="1">
         <v>426</v>
       </c>
-      <c r="B427" s="1">
+      <c r="B427" s="2">
         <v>3044114204</v>
       </c>
-      <c r="C427" s="1">
+      <c r="C427" s="2">
         <v>1871957854</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A428" s="2">
+    <row r="428" spans="1:3">
+      <c r="A428" s="1">
         <v>427</v>
       </c>
-      <c r="B428" s="1">
+      <c r="B428" s="2">
         <v>6182899232</v>
       </c>
-      <c r="C428" s="1">
+      <c r="C428" s="2">
         <v>5323507389</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A429" s="2">
+    <row r="429" spans="1:3">
+      <c r="A429" s="1">
         <v>428</v>
       </c>
-      <c r="B429" s="1">
+      <c r="B429" s="2">
         <v>5415052928</v>
       </c>
-      <c r="C429" s="1">
+      <c r="C429" s="2">
         <v>4501158336</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A430" s="2">
+    <row r="430" spans="1:3">
+      <c r="A430" s="1">
         <v>429</v>
       </c>
-      <c r="B430" s="1">
+      <c r="B430" s="2">
         <v>3860695981</v>
       </c>
-      <c r="C430" s="1">
+      <c r="C430" s="2">
         <v>2435094856</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A431" s="2">
+    <row r="431" spans="1:3">
+      <c r="A431" s="1">
         <v>430</v>
       </c>
-      <c r="B431" s="1">
+      <c r="B431" s="2">
         <v>5695338812</v>
       </c>
-      <c r="C431" s="1">
+      <c r="C431" s="2">
         <v>4553216548</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A432" s="2">
+    <row r="432" spans="1:3">
+      <c r="A432" s="1">
         <v>431</v>
       </c>
-      <c r="B432" s="1">
+      <c r="B432" s="2">
         <v>636491894</v>
       </c>
-      <c r="C432" s="1">
+      <c r="C432" s="2">
         <v>436170927</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A433" s="2">
+    <row r="433" spans="1:3">
+      <c r="A433" s="1">
         <v>432</v>
       </c>
-      <c r="B433" s="1">
+      <c r="B433" s="2">
         <v>2099093467</v>
       </c>
-      <c r="C433" s="1">
+      <c r="C433" s="2">
         <v>1478787199</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A434" s="2">
+    <row r="434" spans="1:3">
+      <c r="A434" s="1">
         <v>433</v>
       </c>
-      <c r="B434" s="1">
+      <c r="B434" s="2">
         <v>3498967518</v>
       </c>
-      <c r="C434" s="1">
+      <c r="C434" s="2">
         <v>2768523129</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A435" s="2">
+    <row r="435" spans="1:3">
+      <c r="A435" s="1">
         <v>434</v>
       </c>
-      <c r="B435" s="1">
+      <c r="B435" s="2">
         <v>5994602282</v>
       </c>
-      <c r="C435" s="1">
+      <c r="C435" s="2">
         <v>3960636371</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A436" s="2">
+    <row r="436" spans="1:3">
+      <c r="A436" s="1">
         <v>435</v>
       </c>
-      <c r="B436" s="1">
+      <c r="B436" s="2">
         <v>6840930948</v>
       </c>
-      <c r="C436" s="1">
+      <c r="C436" s="2">
         <v>5915781395</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A437" s="2">
+    <row r="437" spans="1:3">
+      <c r="A437" s="1">
         <v>436</v>
       </c>
-      <c r="B437" s="1">
+      <c r="B437" s="2">
         <v>5754940995</v>
       </c>
-      <c r="C437" s="1">
+      <c r="C437" s="2">
         <v>398019535</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A438" s="2">
+    <row r="438" spans="1:3">
+      <c r="A438" s="1">
         <v>437</v>
       </c>
-      <c r="B438" s="1">
+      <c r="B438" s="2">
         <v>6926720969</v>
       </c>
-      <c r="C438" s="1">
+      <c r="C438" s="2">
         <v>4708202988</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A439" s="2">
+    <row r="439" spans="1:3">
+      <c r="A439" s="1">
         <v>438</v>
       </c>
-      <c r="B439" s="1">
+      <c r="B439" s="2">
         <v>1623813737</v>
       </c>
-      <c r="C439" s="1">
+      <c r="C439" s="2">
         <v>1416661055</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A440" s="2">
+    <row r="440" spans="1:3">
+      <c r="A440" s="1">
         <v>439</v>
       </c>
-      <c r="B440" s="1">
+      <c r="B440" s="2">
         <v>5906358484</v>
       </c>
-      <c r="C440" s="1">
+      <c r="C440" s="2">
         <v>4328417097</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A441" s="2">
+    <row r="441" spans="1:3">
+      <c r="A441" s="1">
         <v>440</v>
       </c>
-      <c r="B441" s="1">
+      <c r="B441" s="2">
         <v>7481521381</v>
       </c>
-      <c r="C441" s="1">
+      <c r="C441" s="2">
         <v>6196295546</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A442" s="2">
+    <row r="442" spans="1:3">
+      <c r="A442" s="1">
         <v>441</v>
       </c>
-      <c r="B442" s="1">
+      <c r="B442" s="2">
         <v>2607853159</v>
       </c>
-      <c r="C442" s="1">
+      <c r="C442" s="2">
         <v>1945961053</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A443" s="2">
+    <row r="443" spans="1:3">
+      <c r="A443" s="1">
         <v>442</v>
       </c>
-      <c r="B443" s="1">
+      <c r="B443" s="2">
         <v>1660650497</v>
       </c>
-      <c r="C443" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A444" s="2">
+      <c r="C443" s="3">
+        <v>0.698459965</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444" s="1">
         <v>443</v>
       </c>
-      <c r="B444" s="1">
+      <c r="B444" s="2">
         <v>6235585355</v>
       </c>
-      <c r="C444" s="1">
+      <c r="C444" s="2">
         <v>5135455316</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A445" s="2">
+    <row r="445" spans="1:3">
+      <c r="A445" s="1">
         <v>444</v>
       </c>
-      <c r="B445" s="1">
+      <c r="B445" s="2">
         <v>2965991721</v>
       </c>
-      <c r="C445" s="1">
+      <c r="C445" s="2">
         <v>1560355376</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A446" s="2">
+    <row r="446" spans="1:3">
+      <c r="A446" s="1">
         <v>445</v>
       </c>
-      <c r="B446" s="1">
+      <c r="B446" s="2">
         <v>6279265066</v>
       </c>
-      <c r="C446" s="1">
+      <c r="C446" s="2">
         <v>4234991215</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A447" s="2">
+    <row r="447" spans="1:3">
+      <c r="A447" s="1">
         <v>446</v>
       </c>
-      <c r="B447" s="1">
+      <c r="B447" s="2">
         <v>2220403863</v>
       </c>
-      <c r="C447" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A448" s="2">
+      <c r="C447" s="3">
+        <v>0.688909231</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" s="1">
         <v>447</v>
       </c>
-      <c r="B448" s="1">
+      <c r="B448" s="2">
         <v>2070950246</v>
       </c>
-      <c r="C448" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A449" s="2">
+      <c r="C448" s="3">
+        <v>0.685848874</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449" s="1">
         <v>448</v>
       </c>
-      <c r="B449" s="1">
+      <c r="B449" s="2">
         <v>2868418626</v>
       </c>
-      <c r="C449" s="1">
+      <c r="C449" s="2">
         <v>1791753568</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A450" s="2">
+    <row r="450" spans="1:3">
+      <c r="A450" s="1">
         <v>449</v>
       </c>
-      <c r="B450" s="1">
+      <c r="B450" s="2">
         <v>3928140904</v>
       </c>
-      <c r="C450" s="1">
+      <c r="C450" s="2">
         <v>3227472173</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A451" s="2">
+    <row r="451" spans="1:3">
+      <c r="A451" s="1">
         <v>450</v>
       </c>
-      <c r="B451" s="1">
+      <c r="B451" s="2">
         <v>6835747726</v>
       </c>
-      <c r="C451" s="1">
+      <c r="C451" s="2">
         <v>515933124</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A452" s="2">
+    <row r="452" spans="1:3">
+      <c r="A452" s="1">
         <v>451</v>
       </c>
-      <c r="B452" s="1">
+      <c r="B452" s="2">
         <v>3437164722</v>
       </c>
-      <c r="C452" s="1">
+      <c r="C452" s="2">
         <v>3802970673</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A453" s="2">
+    <row r="453" spans="1:3">
+      <c r="A453" s="1">
         <v>452</v>
       </c>
-      <c r="B453" s="1">
+      <c r="B453" s="2">
         <v>5299565218</v>
       </c>
-      <c r="C453" s="1">
+      <c r="C453" s="2">
         <v>4216057592</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A454" s="2">
+    <row r="454" spans="1:3">
+      <c r="A454" s="1">
         <v>453</v>
       </c>
-      <c r="B454" s="1">
+      <c r="B454" s="2">
         <v>6004521296</v>
       </c>
-      <c r="C454" s="1">
+      <c r="C454" s="2">
         <v>4932409978</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A455" s="2">
+    <row r="455" spans="1:3">
+      <c r="A455" s="1">
         <v>454</v>
       </c>
-      <c r="B455" s="1">
+      <c r="B455" s="2">
         <v>3283166895</v>
       </c>
-      <c r="C455" s="1">
+      <c r="C455" s="2">
         <v>2233440584</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A456" s="2">
+    <row r="456" spans="1:3">
+      <c r="A456" s="1">
         <v>455</v>
       </c>
-      <c r="B456" s="1">
+      <c r="B456" s="2">
         <v>5919129259</v>
       </c>
-      <c r="C456" s="1">
+      <c r="C456" s="2">
         <v>437825945</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A457" s="2">
+    <row r="457" spans="1:3">
+      <c r="A457" s="1">
         <v>456</v>
       </c>
-      <c r="B457" s="1">
+      <c r="B457" s="2">
         <v>3910198547</v>
       </c>
-      <c r="C457" s="1">
+      <c r="C457" s="2">
         <v>3483925685</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A458" s="2">
+    <row r="458" spans="1:3">
+      <c r="A458" s="1">
         <v>457</v>
       </c>
-      <c r="B458" s="1">
+      <c r="B458" s="2">
         <v>2642098592</v>
       </c>
-      <c r="C458" s="1">
+      <c r="C458" s="2">
         <v>2030297043</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A459" s="2">
+    <row r="459" spans="1:3">
+      <c r="A459" s="1">
         <v>458</v>
       </c>
-      <c r="B459" s="1">
+      <c r="B459" s="2">
         <v>5720877412</v>
       </c>
-      <c r="C459" s="1">
+      <c r="C459" s="2">
         <v>3596398318</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A460" s="2">
+    <row r="460" spans="1:3">
+      <c r="A460" s="1">
         <v>459</v>
       </c>
-      <c r="B460" s="1">
+      <c r="B460" s="2">
         <v>339991642</v>
       </c>
-      <c r="C460" s="1">
+      <c r="C460" s="2">
         <v>3261182104</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A461" s="2">
+    <row r="461" spans="1:3">
+      <c r="A461" s="1">
         <v>460</v>
       </c>
-      <c r="B461" s="1">
+      <c r="B461" s="2">
         <v>1611606313</v>
       </c>
-      <c r="C461" s="1">
+      <c r="C461" s="2">
         <v>3481137767</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A462" s="2">
+    <row r="462" spans="1:3">
+      <c r="A462" s="1">
         <v>461</v>
       </c>
-      <c r="B462" s="1">
+      <c r="B462" s="2">
         <v>478368549</v>
       </c>
-      <c r="C462" s="1">
+      <c r="C462" s="2">
         <v>3393439153</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A463" s="2">
+    <row r="463" spans="1:3">
+      <c r="A463" s="1">
         <v>462</v>
       </c>
-      <c r="B463" s="1">
+      <c r="B463" s="2">
         <v>4591489106</v>
       </c>
-      <c r="C463" s="1">
+      <c r="C463" s="2">
         <v>4229663345</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A464" s="2">
+    <row r="464" spans="1:3">
+      <c r="A464" s="1">
         <v>463</v>
       </c>
-      <c r="B464" s="1">
+      <c r="B464" s="2">
         <v>5671839739</v>
       </c>
-      <c r="C464" s="1">
+      <c r="C464" s="2">
         <v>4321364297</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A465" s="2">
+    <row r="465" spans="1:3">
+      <c r="A465" s="1">
         <v>464</v>
       </c>
-      <c r="B465" s="1">
+      <c r="B465" s="2">
         <v>6052731401</v>
       </c>
-      <c r="C465" s="1">
+      <c r="C465" s="2">
         <v>4400455145</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A466" s="2">
+    <row r="466" spans="1:3">
+      <c r="A466" s="1">
         <v>465</v>
       </c>
-      <c r="B466" s="1">
+      <c r="B466" s="2">
         <v>4215794177</v>
       </c>
-      <c r="C466" s="1">
+      <c r="C466" s="2">
         <v>3357597382</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A467" s="2">
+    <row r="467" spans="1:3">
+      <c r="A467" s="1">
         <v>466</v>
       </c>
-      <c r="B467" s="1">
+      <c r="B467" s="2">
         <v>6495854763</v>
       </c>
-      <c r="C467" s="1">
+      <c r="C467" s="2">
         <v>5335718004</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A468" s="2">
+    <row r="468" spans="1:3">
+      <c r="A468" s="1">
         <v>467</v>
       </c>
-      <c r="B468" s="1">
+      <c r="B468" s="2">
         <v>6546132584</v>
       </c>
-      <c r="C468" s="1">
+      <c r="C468" s="2">
         <v>5588389336</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A469" s="2">
+    <row r="469" spans="1:3">
+      <c r="A469" s="1">
         <v>468</v>
       </c>
-      <c r="B469" s="1">
+      <c r="B469" s="2">
         <v>4688219626</v>
       </c>
-      <c r="C469" s="1">
+      <c r="C469" s="2">
         <v>2994204284</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A470" s="2">
+    <row r="470" spans="1:3">
+      <c r="A470" s="1">
         <v>469</v>
       </c>
-      <c r="B470" s="1">
+      <c r="B470" s="2">
         <v>3126524031</v>
       </c>
-      <c r="C470" s="1">
+      <c r="C470" s="2">
         <v>2413381753</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A471" s="2">
+    <row r="471" spans="1:3">
+      <c r="A471" s="1">
         <v>470</v>
       </c>
-      <c r="B471" s="1">
+      <c r="B471" s="2">
         <v>6781564124</v>
       </c>
-      <c r="C471" s="1">
+      <c r="C471" s="2">
         <v>498536659</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A472" s="2">
+    <row r="472" spans="1:3">
+      <c r="A472" s="1">
         <v>471</v>
       </c>
-      <c r="B472" s="1">
+      <c r="B472" s="2">
         <v>7119505376</v>
       </c>
-      <c r="C472" s="1">
+      <c r="C472" s="2">
         <v>4981981125</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A473" s="2">
+    <row r="473" spans="1:3">
+      <c r="A473" s="1">
         <v>472</v>
       </c>
-      <c r="B473" s="1">
+      <c r="B473" s="2">
         <v>7297722283</v>
       </c>
-      <c r="C473" s="1">
+      <c r="C473" s="2">
         <v>6384274497</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A474" s="2">
+    <row r="474" spans="1:3">
+      <c r="A474" s="1">
         <v>473</v>
       </c>
-      <c r="B474" s="1">
+      <c r="B474" s="2">
         <v>6273493543</v>
       </c>
-      <c r="C474" s="1">
+      <c r="C474" s="2">
         <v>326747544</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A475" s="2">
+    <row r="475" spans="1:3">
+      <c r="A475" s="1">
         <v>474</v>
       </c>
-      <c r="B475" s="1">
+      <c r="B475" s="2">
         <v>1587315346</v>
       </c>
-      <c r="C475" s="1">
+      <c r="C475" s="2">
         <v>1312758977</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A476" s="2">
+    <row r="476" spans="1:3">
+      <c r="A476" s="1">
         <v>475</v>
       </c>
-      <c r="B476" s="1">
+      <c r="B476" s="2">
         <v>6001806863</v>
       </c>
-      <c r="C476" s="1">
+      <c r="C476" s="2">
         <v>4039547986</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A477" s="2">
+    <row r="477" spans="1:3">
+      <c r="A477" s="1">
         <v>476</v>
       </c>
-      <c r="B477" s="1">
+      <c r="B477" s="2">
         <v>5723226096</v>
       </c>
-      <c r="C477" s="1">
+      <c r="C477" s="2">
         <v>4425995084</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A478" s="2">
+    <row r="478" spans="1:3">
+      <c r="A478" s="1">
         <v>477</v>
       </c>
-      <c r="B478" s="1">
+      <c r="B478" s="2">
         <v>5237893052</v>
       </c>
-      <c r="C478" s="1">
+      <c r="C478" s="2">
         <v>3342749396</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A479" s="2">
+    <row r="479" spans="1:3">
+      <c r="A479" s="1">
         <v>478</v>
       </c>
-      <c r="B479" s="1">
+      <c r="B479" s="2">
         <v>598994534</v>
       </c>
-      <c r="C479" s="1">
+      <c r="C479" s="2">
         <v>3492310186</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A480" s="2">
+    <row r="480" spans="1:3">
+      <c r="A480" s="1">
         <v>479</v>
       </c>
-      <c r="B480" s="1">
+      <c r="B480" s="2">
         <v>4272336668</v>
       </c>
-      <c r="C480" s="1">
+      <c r="C480" s="2">
         <v>3751225463</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A481" s="2">
+    <row r="481" spans="1:3">
+      <c r="A481" s="1">
         <v>480</v>
       </c>
-      <c r="B481" s="1">
+      <c r="B481" s="2">
         <v>652277168</v>
       </c>
-      <c r="C481" s="1">
+      <c r="C481" s="2">
         <v>5386559329</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A482" s="2">
+    <row r="482" spans="1:3">
+      <c r="A482" s="1">
         <v>481</v>
       </c>
-      <c r="B482" s="1">
+      <c r="B482" s="2">
         <v>7448116557</v>
       </c>
-      <c r="C482" s="1">
+      <c r="C482" s="2">
         <v>5963422086</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A483" s="2">
+    <row r="483" spans="1:3">
+      <c r="A483" s="1">
         <v>482</v>
       </c>
-      <c r="B483" s="1">
+      <c r="B483" s="2">
         <v>7225191864</v>
       </c>
-      <c r="C483" s="1">
+      <c r="C483" s="2">
         <v>4985254927</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A484" s="2">
+    <row r="484" spans="1:3">
+      <c r="A484" s="1">
         <v>483</v>
       </c>
-      <c r="B484" s="1">
+      <c r="B484" s="2">
         <v>3275334807</v>
       </c>
-      <c r="C484" s="1">
+      <c r="C484" s="2">
         <v>2798160728</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A485" s="2">
+    <row r="485" spans="1:3">
+      <c r="A485" s="1">
         <v>484</v>
       </c>
-      <c r="B485" s="1">
+      <c r="B485" s="2">
         <v>2021817764</v>
       </c>
-      <c r="C485" s="1">
+      <c r="C485" s="2">
         <v>2967323268</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A486" s="2">
+    <row r="486" spans="1:3">
+      <c r="A486" s="1">
         <v>485</v>
       </c>
-      <c r="B486" s="1">
+      <c r="B486" s="2">
         <v>2840140748</v>
       </c>
-      <c r="C486" s="1">
+      <c r="C486" s="2">
         <v>1228773184</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A487" s="2">
+    <row r="487" spans="1:3">
+      <c r="A487" s="1">
         <v>486</v>
       </c>
-      <c r="B487" s="1">
+      <c r="B487" s="2">
         <v>6101564703</v>
       </c>
-      <c r="C487" s="1">
+      <c r="C487" s="2">
         <v>396172964</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A488" s="2">
+    <row r="488" spans="1:3">
+      <c r="A488" s="1">
         <v>487</v>
       </c>
-      <c r="B488" s="1">
+      <c r="B488" s="2">
         <v>6074327799</v>
       </c>
-      <c r="C488" s="1">
+      <c r="C488" s="2">
         <v>4649143652</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A489" s="2">
+    <row r="489" spans="1:3">
+      <c r="A489" s="1">
         <v>488</v>
       </c>
-      <c r="B489" s="1">
+      <c r="B489" s="2">
         <v>4243872552</v>
       </c>
-      <c r="C489" s="1">
+      <c r="C489" s="2">
         <v>4754168395</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A490" s="2">
+    <row r="490" spans="1:3">
+      <c r="A490" s="1">
         <v>489</v>
       </c>
-      <c r="B490" s="1">
+      <c r="B490" s="2">
         <v>5328575592</v>
       </c>
-      <c r="C490" s="1">
+      <c r="C490" s="2">
         <v>2961956663</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A491" s="2">
+    <row r="491" spans="1:3">
+      <c r="A491" s="1">
         <v>490</v>
       </c>
-      <c r="B491" s="1">
+      <c r="B491" s="2">
         <v>6052381321</v>
       </c>
-      <c r="C491" s="1">
+      <c r="C491" s="2">
         <v>4633441055</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A492" s="2">
+    <row r="492" spans="1:3">
+      <c r="A492" s="1">
         <v>491</v>
       </c>
-      <c r="B492" s="1">
+      <c r="B492" s="2">
         <v>3154042591</v>
       </c>
-      <c r="C492" s="1">
+      <c r="C492" s="2">
         <v>1294136576</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A493" s="2">
+    <row r="493" spans="1:3">
+      <c r="A493" s="1">
         <v>492</v>
       </c>
-      <c r="B493" s="1">
+      <c r="B493" s="2">
         <v>2682381605</v>
       </c>
-      <c r="C493" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A494" s="2">
+      <c r="C493" s="3">
+        <v>0.548365189</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494" s="1">
         <v>493</v>
       </c>
-      <c r="B494" s="1">
+      <c r="B494" s="2">
         <v>3435101751</v>
       </c>
-      <c r="C494" s="1">
+      <c r="C494" s="2">
         <v>2115136485</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A495" s="2">
+    <row r="495" spans="1:3">
+      <c r="A495" s="1">
         <v>494</v>
       </c>
-      <c r="B495" s="1">
+      <c r="B495" s="2">
         <v>5349208789</v>
       </c>
-      <c r="C495" s="1">
+      <c r="C495" s="2">
         <v>456870456</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A496" s="2">
+    <row r="496" spans="1:3">
+      <c r="A496" s="1">
         <v>495</v>
       </c>
-      <c r="B496" s="1">
+      <c r="B496" s="2">
         <v>3471798585</v>
       </c>
-      <c r="C496" s="1">
+      <c r="C496" s="2">
         <v>2535002113</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A497" s="2">
+    <row r="497" spans="1:3">
+      <c r="A497" s="1">
         <v>496</v>
       </c>
-      <c r="B497" s="1">
+      <c r="B497" s="2">
         <v>6097609623</v>
       </c>
-      <c r="C497" s="1">
+      <c r="C497" s="2">
         <v>4397451275</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A498" s="2">
+    <row r="498" spans="1:3">
+      <c r="A498" s="1">
         <v>497</v>
       </c>
-      <c r="B498" s="1">
+      <c r="B498" s="2">
         <v>3440846876</v>
       </c>
-      <c r="C498" s="1">
+      <c r="C498" s="2">
         <v>2070663768</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A499" s="2">
+    <row r="499" spans="1:3">
+      <c r="A499" s="1">
         <v>498</v>
       </c>
-      <c r="B499" s="1">
+      <c r="B499" s="2">
         <v>4530545407</v>
       </c>
-      <c r="C499" s="1">
+      <c r="C499" s="2">
         <v>3710192978</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>